--- a/data/Heat map 7.xlsx
+++ b/data/Heat map 7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF4D828-AD04-4F7D-92F6-990B077FA456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E0E4538-D847-4D07-B164-C69148507C4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{462AB6D2-C8E4-47A1-AF79-F15809A5475A}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Reputation, Society" sheetId="1" r:id="rId1"/>
@@ -23,10 +23,8 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Reputation, Society'!$B$1:$L$17</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -54,28 +52,28 @@
     <t>Society Impact &amp; Inclusion</t>
   </si>
   <si>
-    <t>Number of active collaborations with scaling partners</t>
-  </si>
-  <si>
-    <t>Number of awards granted to IITA staff/project teams</t>
-  </si>
-  <si>
-    <t>Number of invitations to IITA staff to give seminars, as guest speakers etc.</t>
-  </si>
-  <si>
-    <t>Number of direct engagements  with senior policymakers to provide strategic advice, influence reforms, or shape national strategies.</t>
-  </si>
-  <si>
-    <t>Approved proposals with gender/youth/social inclusion components (target is 25% of total approved proposals)</t>
-  </si>
-  <si>
-    <t>Approved proposals with inclusion of adaptation/ mitigation activities  (target is 25% of total approved proposals)</t>
-  </si>
-  <si>
-    <t>Approved proposals with inclusion of nutrition and health activities (target is 25% of total approved proposals)</t>
-  </si>
-  <si>
-    <t>Number of collaborations with ARIs</t>
+    <t>ARIs collaborations</t>
+  </si>
+  <si>
+    <t>Active collaborations with scaling partners</t>
+  </si>
+  <si>
+    <t>Awards grated to IITA stafff</t>
+  </si>
+  <si>
+    <t>Invitations to give seminars/talks</t>
+  </si>
+  <si>
+    <t>High level engagements</t>
+  </si>
+  <si>
+    <t>Approved proposals with GeYSI components</t>
+  </si>
+  <si>
+    <t>Approved proposals with climate components</t>
+  </si>
+  <si>
+    <t>Approved proposals with nutrition and health components</t>
   </si>
   <si>
     <t>GI</t>
@@ -137,12 +135,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -273,7 +271,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="35">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -300,71 +298,32 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="thin">
@@ -544,19 +503,6 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF00B050"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF00B050"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
       <right style="medium">
         <color theme="1"/>
       </right>
@@ -582,19 +528,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF00B050"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -683,17 +616,6 @@
         <color indexed="64"/>
       </left>
       <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top/>
       <bottom/>
       <diagonal/>
@@ -739,113 +661,163 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF00B050"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="19" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -854,16 +826,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -875,57 +847,32 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -948,9 +895,6 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Chart1"/>
       <sheetName val="Sheet1"/>
@@ -1347,13 +1291,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B652AA3-1E8A-41A7-8E84-C9E5096ACF8A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:AF23"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="3.21875" style="26" customWidth="1"/>
     <col min="3" max="3" width="26.77734375" style="26" customWidth="1"/>
@@ -1368,37 +1312,37 @@
     <col min="14" max="18" width="8.21875" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" ht="15" thickBot="1">
+    <row r="1" spans="2:18" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1"/>
-      <c r="C1" s="58" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="59"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="61"/>
-      <c r="K1" s="62"/>
+      <c r="C1" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="54"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
     </row>
-    <row r="2" spans="2:18" s="7" customFormat="1" ht="25.95" customHeight="1" thickBot="1">
+    <row r="2" spans="2:18" s="7" customFormat="1" ht="25.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="5"/>
       <c r="C2" s="4"/>
-      <c r="D2" s="63" t="s">
+      <c r="D2" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="66" t="s">
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="66"/>
-      <c r="K2" s="67"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="56"/>
       <c r="L2" s="6"/>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
@@ -1407,32 +1351,32 @@
       <c r="Q2" s="6"/>
       <c r="R2" s="6"/>
     </row>
-    <row r="3" spans="2:18" s="17" customFormat="1" ht="132" customHeight="1" thickBot="1">
+    <row r="3" spans="2:18" s="17" customFormat="1" ht="132" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1"/>
       <c r="C3" s="11"/>
       <c r="D3" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="10" t="s">
         <v>10</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="K3" s="10" t="s">
-        <v>9</v>
       </c>
       <c r="L3" s="15"/>
       <c r="M3" s="15"/>
@@ -1442,8 +1386,8 @@
       <c r="Q3" s="16"/>
       <c r="R3" s="16"/>
     </row>
-    <row r="4" spans="2:18" s="27" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B4" s="55" t="s">
+    <row r="4" spans="2:18" s="27" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="57" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="18" t="s">
@@ -1480,13 +1424,13 @@
       <c r="Q4" s="26"/>
       <c r="R4" s="26"/>
     </row>
-    <row r="5" spans="2:18" s="27" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B5" s="56"/>
+    <row r="5" spans="2:18" s="27" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="58"/>
       <c r="C5" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D5" s="19">
-        <v>1.8081164242580787</v>
+        <v>1.8081164242580789</v>
       </c>
       <c r="E5" s="20" t="s">
         <v>13</v>
@@ -1495,7 +1439,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="20">
-        <v>0.23584127272931465</v>
+        <v>0.23584127272931471</v>
       </c>
       <c r="H5" s="22"/>
       <c r="I5" s="23">
@@ -1518,8 +1462,8 @@
       <c r="Q5" s="26"/>
       <c r="R5" s="26"/>
     </row>
-    <row r="6" spans="2:18" s="27" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B6" s="56"/>
+    <row r="6" spans="2:18" s="27" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="58"/>
       <c r="C6" s="28" t="s">
         <v>15</v>
       </c>
@@ -1553,8 +1497,8 @@
       <c r="Q6" s="26"/>
       <c r="R6" s="26"/>
     </row>
-    <row r="7" spans="2:18" s="27" customFormat="1" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B7" s="57"/>
+    <row r="7" spans="2:18" s="27" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="59"/>
       <c r="C7" s="30" t="s">
         <v>16</v>
       </c>
@@ -1592,18 +1536,18 @@
       <c r="Q7" s="26"/>
       <c r="R7" s="26"/>
     </row>
-    <row r="8" spans="2:18" s="27" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B8" s="55" t="s">
+    <row r="8" spans="2:18" s="27" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="57" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="18" t="s">
         <v>18</v>
       </c>
       <c r="D8" s="19">
-        <v>2.3312594543872254</v>
+        <v>2.3312594543872249</v>
       </c>
       <c r="E8" s="20">
-        <v>0.12951441413262363</v>
+        <v>0.1295144141326236</v>
       </c>
       <c r="F8" s="21">
         <f>[1]Sheet1!$AD$18</f>
@@ -1632,22 +1576,22 @@
       <c r="Q8" s="26"/>
       <c r="R8" s="26"/>
     </row>
-    <row r="9" spans="2:18" s="27" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B9" s="56"/>
+    <row r="9" spans="2:18" s="27" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="58"/>
       <c r="C9" s="35" t="s">
         <v>19</v>
       </c>
       <c r="D9" s="19">
-        <v>3.5035776248709567</v>
+        <v>3.5035776248709571</v>
       </c>
       <c r="E9" s="20">
-        <v>1.3851353400652622</v>
+        <v>1.385135340065262</v>
       </c>
       <c r="F9" s="21">
         <v>0</v>
       </c>
       <c r="G9" s="20">
-        <v>0.24443564824681097</v>
+        <v>0.24443564824681099</v>
       </c>
       <c r="H9" s="22"/>
       <c r="I9" s="23">
@@ -1670,8 +1614,8 @@
       <c r="Q9" s="26"/>
       <c r="R9" s="26"/>
     </row>
-    <row r="10" spans="2:18" s="27" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B10" s="56"/>
+    <row r="10" spans="2:18" s="27" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="58"/>
       <c r="C10" s="28" t="s">
         <v>20</v>
       </c>
@@ -1707,8 +1651,8 @@
       <c r="Q10" s="26"/>
       <c r="R10" s="26"/>
     </row>
-    <row r="11" spans="2:18" s="27" customFormat="1" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B11" s="57"/>
+    <row r="11" spans="2:18" s="27" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="59"/>
       <c r="C11" s="30" t="s">
         <v>21</v>
       </c>
@@ -1742,8 +1686,8 @@
       <c r="Q11" s="26"/>
       <c r="R11" s="26"/>
     </row>
-    <row r="12" spans="2:18" s="27" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B12" s="52" t="s">
+    <row r="12" spans="2:18" s="27" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="63" t="s">
         <v>22</v>
       </c>
       <c r="C12" s="18" t="s">
@@ -1779,8 +1723,8 @@
       <c r="Q12" s="26"/>
       <c r="R12" s="26"/>
     </row>
-    <row r="13" spans="2:18" s="27" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B13" s="53"/>
+    <row r="13" spans="2:18" s="27" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="58"/>
       <c r="C13" s="28" t="s">
         <v>24</v>
       </c>
@@ -1794,7 +1738,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="20">
-        <v>0.39807039262342825</v>
+        <v>0.39807039262342819</v>
       </c>
       <c r="H13" s="22"/>
       <c r="I13" s="23">
@@ -1814,22 +1758,22 @@
       <c r="Q13" s="26"/>
       <c r="R13" s="26"/>
     </row>
-    <row r="14" spans="2:18" s="27" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B14" s="53"/>
+    <row r="14" spans="2:18" s="27" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="58"/>
       <c r="C14" s="28" t="s">
         <v>25</v>
       </c>
       <c r="D14" s="19">
-        <v>2.8228572396408196</v>
+        <v>2.82285723964082</v>
       </c>
       <c r="E14" s="20">
-        <v>1.4114286198204098</v>
+        <v>1.41142861982041</v>
       </c>
       <c r="F14" s="21">
         <v>0</v>
       </c>
       <c r="G14" s="20">
-        <v>1.4114286198204098</v>
+        <v>1.41142861982041</v>
       </c>
       <c r="H14" s="22"/>
       <c r="I14" s="23">
@@ -1849,8 +1793,8 @@
       <c r="Q14" s="26"/>
       <c r="R14" s="26"/>
     </row>
-    <row r="15" spans="2:18" s="27" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B15" s="53"/>
+    <row r="15" spans="2:18" s="27" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="58"/>
       <c r="C15" s="28" t="s">
         <v>26</v>
       </c>
@@ -1884,8 +1828,8 @@
       <c r="Q15" s="26"/>
       <c r="R15" s="26"/>
     </row>
-    <row r="16" spans="2:18" s="27" customFormat="1" ht="15.45" customHeight="1" thickBot="1">
-      <c r="B16" s="54"/>
+    <row r="16" spans="2:18" s="27" customFormat="1" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="64"/>
       <c r="C16" s="36" t="s">
         <v>27</v>
       </c>
@@ -1921,7 +1865,7 @@
       <c r="Q16" s="26"/>
       <c r="R16" s="26"/>
     </row>
-    <row r="17" spans="2:32" s="44" customFormat="1">
+    <row r="17" spans="2:32" s="44" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B17" s="41"/>
       <c r="C17" s="45" t="s">
         <v>28</v>
@@ -1940,13 +1884,13 @@
       </c>
       <c r="H17" s="42"/>
       <c r="I17" s="47">
-        <v>2.8744446786796956E-3</v>
+        <v>2.8744446786796961E-3</v>
       </c>
       <c r="J17" s="47">
-        <v>2.8744446786796956E-3</v>
+        <v>2.8744446786796961E-3</v>
       </c>
       <c r="K17" s="47">
-        <v>2.8744446786796956E-3</v>
+        <v>2.8744446786796961E-3</v>
       </c>
       <c r="L17" s="43"/>
       <c r="M17" s="43"/>
@@ -1970,28 +1914,28 @@
       <c r="AE17" s="43"/>
       <c r="AF17" s="43"/>
     </row>
-    <row r="19" spans="2:32" hidden="1">
+    <row r="19" spans="2:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="C19" s="49"/>
       <c r="D19" s="50"/>
     </row>
-    <row r="20" spans="2:32" hidden="1">
+    <row r="20" spans="2:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="C20" s="40"/>
       <c r="D20" s="48"/>
     </row>
-    <row r="21" spans="2:32" hidden="1">
+    <row r="21" spans="2:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="C21" s="48"/>
       <c r="D21" s="48"/>
     </row>
-    <row r="22" spans="2:32" hidden="1"/>
-    <row r="23" spans="2:32" hidden="1"/>
+    <row r="22" spans="2:32" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="2:32" hidden="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="B12:B16"/>
+    <mergeCell ref="C1:K1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="D2:H2"/>
     <mergeCell ref="B4:B7"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="C1:K1"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="I2:K2"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:D16">
     <cfRule type="colorScale" priority="1">
@@ -2220,7 +2164,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="8" scale="88" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="8" scale="88" orientation="landscape"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="2" max="18" man="1"/>
   </colBreaks>

--- a/data/Heat map 7.xlsx
+++ b/data/Heat map 7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E0E4538-D847-4D07-B164-C69148507C4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BDB2520-0E5C-494E-9816-FE88C2A17811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,6 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Reputation, Society'!$B$1:$L$17</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -850,6 +849,11 @@
     <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -862,17 +866,12 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -896,12 +895,68 @@
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
+      <sheetName val="PR 1"/>
+      <sheetName val="PR 2"/>
+      <sheetName val="PR 3"/>
+      <sheetName val="PR 4"/>
+      <sheetName val="PR 5"/>
+      <sheetName val="PR 6"/>
+      <sheetName val="PR 7"/>
+      <sheetName val="PR 8"/>
+      <sheetName val="PR 9"/>
+      <sheetName val="PR 10"/>
+      <sheetName val="PR 11"/>
+      <sheetName val="PR 12"/>
+      <sheetName val="PR 13"/>
+      <sheetName val="PR 14"/>
+      <sheetName val="PR15"/>
+      <sheetName val="PR 16"/>
+      <sheetName val="PR 18"/>
+      <sheetName val="PR 19"/>
+      <sheetName val="PR20"/>
       <sheetName val="Chart1"/>
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7">
+        <row r="4">
+          <cell r="G4">
+            <v>0.65217391304347827</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="8">
+        <row r="4">
+          <cell r="G4">
+            <v>6.521739130434782E-4</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="9">
+        <row r="5">
+          <cell r="G5">
+            <v>0.25</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20">
         <row r="12">
           <cell r="I12">
             <v>1.4999999999999999E-2</v>
@@ -921,26 +976,6 @@
             <v>0.17242666505128171</v>
           </cell>
         </row>
-        <row r="21">
-          <cell r="X21">
-            <v>0.15722751515287642</v>
-          </cell>
-          <cell r="AB21">
-            <v>0.14081259645953281</v>
-          </cell>
-          <cell r="AD21">
-            <v>0.12951441413262363</v>
-          </cell>
-          <cell r="AF21">
-            <v>0.32591419766241464</v>
-          </cell>
-          <cell r="AH21">
-            <v>0.55694906946705569</v>
-          </cell>
-          <cell r="AT21">
-            <v>0.17242666505128171</v>
-          </cell>
-        </row>
         <row r="22">
           <cell r="X22">
             <v>7.8613757576438209E-2</v>
@@ -950,12 +985,6 @@
           </cell>
           <cell r="AD22">
             <v>0.12951441413262363</v>
-          </cell>
-          <cell r="AF22">
-            <v>0.32591419766241464</v>
-          </cell>
-          <cell r="AH22">
-            <v>0.6961863368338197</v>
           </cell>
         </row>
         <row r="23">
@@ -1314,35 +1343,35 @@
   <sheetData>
     <row r="1" spans="2:18" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1"/>
-      <c r="C1" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="54"/>
+      <c r="C1" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="57"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
     </row>
     <row r="2" spans="2:18" s="7" customFormat="1" ht="25.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="5"/>
       <c r="C2" s="4"/>
-      <c r="D2" s="60" t="s">
+      <c r="D2" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="55" t="s">
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="53"/>
-      <c r="K2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="59"/>
       <c r="L2" s="6"/>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
@@ -1387,7 +1416,7 @@
       <c r="R3" s="16"/>
     </row>
     <row r="4" spans="2:18" s="27" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="57" t="s">
+      <c r="B4" s="60" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="18" t="s">
@@ -1425,7 +1454,7 @@
       <c r="R4" s="26"/>
     </row>
     <row r="5" spans="2:18" s="27" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="58"/>
+      <c r="B5" s="53"/>
       <c r="C5" s="28" t="s">
         <v>14</v>
       </c>
@@ -1443,8 +1472,7 @@
       </c>
       <c r="H5" s="22"/>
       <c r="I5" s="23">
-        <f>[1]Sheet1!$X$21</f>
-        <v>0.15722751515287642</v>
+        <v>0.157</v>
       </c>
       <c r="J5" s="29">
         <f>[1]Sheet1!$X$22</f>
@@ -1463,7 +1491,7 @@
       <c r="R5" s="26"/>
     </row>
     <row r="6" spans="2:18" s="27" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="58"/>
+      <c r="B6" s="53"/>
       <c r="C6" s="28" t="s">
         <v>15</v>
       </c>
@@ -1498,7 +1526,7 @@
       <c r="R6" s="26"/>
     </row>
     <row r="7" spans="2:18" s="27" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="59"/>
+      <c r="B7" s="61"/>
       <c r="C7" s="30" t="s">
         <v>16</v>
       </c>
@@ -1517,8 +1545,7 @@
       </c>
       <c r="H7" s="22"/>
       <c r="I7" s="31">
-        <f>[1]Sheet1!$AB$21</f>
-        <v>0.14081259645953281</v>
+        <v>0.14099999999999999</v>
       </c>
       <c r="J7" s="32">
         <f>[1]Sheet1!$AB$22</f>
@@ -1537,7 +1564,7 @@
       <c r="R7" s="26"/>
     </row>
     <row r="8" spans="2:18" s="27" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="57" t="s">
+      <c r="B8" s="60" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="18" t="s">
@@ -1558,8 +1585,7 @@
       </c>
       <c r="H8" s="22"/>
       <c r="I8" s="34">
-        <f>[1]Sheet1!$AD$21</f>
-        <v>0.12951441413262363</v>
+        <v>0.13</v>
       </c>
       <c r="J8" s="24">
         <f>[1]Sheet1!$AD$22</f>
@@ -1577,7 +1603,7 @@
       <c r="R8" s="26"/>
     </row>
     <row r="9" spans="2:18" s="27" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="58"/>
+      <c r="B9" s="53"/>
       <c r="C9" s="35" t="s">
         <v>19</v>
       </c>
@@ -1595,12 +1621,10 @@
       </c>
       <c r="H9" s="22"/>
       <c r="I9" s="23">
-        <f>[1]Sheet1!$AF$21</f>
-        <v>0.32591419766241464</v>
+        <v>0.32600000000000001</v>
       </c>
       <c r="J9" s="29">
-        <f>[1]Sheet1!$AF$22</f>
-        <v>0.32591419766241464</v>
+        <v>0.32600000000000001</v>
       </c>
       <c r="K9" s="22">
         <f>[1]Sheet1!$AF$23</f>
@@ -1615,7 +1639,7 @@
       <c r="R9" s="26"/>
     </row>
     <row r="10" spans="2:18" s="27" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="58"/>
+      <c r="B10" s="53"/>
       <c r="C10" s="28" t="s">
         <v>20</v>
       </c>
@@ -1633,12 +1657,10 @@
       </c>
       <c r="H10" s="22"/>
       <c r="I10" s="23">
-        <f>[1]Sheet1!$AH$21</f>
-        <v>0.55694906946705569</v>
+        <v>0.55700000000000005</v>
       </c>
       <c r="J10" s="29">
-        <f>[1]Sheet1!$AH$22</f>
-        <v>0.6961863368338197</v>
+        <v>0.69599999999999995</v>
       </c>
       <c r="K10" s="22">
         <v>0</v>
@@ -1652,7 +1674,7 @@
       <c r="R10" s="26"/>
     </row>
     <row r="11" spans="2:18" s="27" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="59"/>
+      <c r="B11" s="61"/>
       <c r="C11" s="30" t="s">
         <v>21</v>
       </c>
@@ -1687,7 +1709,7 @@
       <c r="R11" s="26"/>
     </row>
     <row r="12" spans="2:18" s="27" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="63" t="s">
+      <c r="B12" s="52" t="s">
         <v>22</v>
       </c>
       <c r="C12" s="18" t="s">
@@ -1724,7 +1746,7 @@
       <c r="R12" s="26"/>
     </row>
     <row r="13" spans="2:18" s="27" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="58"/>
+      <c r="B13" s="53"/>
       <c r="C13" s="28" t="s">
         <v>24</v>
       </c>
@@ -1759,7 +1781,7 @@
       <c r="R13" s="26"/>
     </row>
     <row r="14" spans="2:18" s="27" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="58"/>
+      <c r="B14" s="53"/>
       <c r="C14" s="28" t="s">
         <v>25</v>
       </c>
@@ -1794,7 +1816,7 @@
       <c r="R14" s="26"/>
     </row>
     <row r="15" spans="2:18" s="27" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="58"/>
+      <c r="B15" s="53"/>
       <c r="C15" s="28" t="s">
         <v>26</v>
       </c>
@@ -1829,7 +1851,7 @@
       <c r="R15" s="26"/>
     </row>
     <row r="16" spans="2:18" s="27" customFormat="1" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="64"/>
+      <c r="B16" s="54"/>
       <c r="C16" s="36" t="s">
         <v>27</v>
       </c>
@@ -1848,8 +1870,7 @@
       </c>
       <c r="H16" s="33"/>
       <c r="I16" s="31">
-        <f>[1]Sheet1!$AT$21</f>
-        <v>0.17242666505128171</v>
+        <v>0.17199999999999999</v>
       </c>
       <c r="J16" s="32">
         <v>0</v>

--- a/data/Heat map 7.xlsx
+++ b/data/Heat map 7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0321BAA-5E6F-4E8A-BA00-81DBEC62E9B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74E36548-B354-4D67-A62E-93A33D3D59F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{462AB6D2-C8E4-47A1-AF79-F15809A5475A}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   </externalReferences>
   <definedNames>
     <definedName name="_Hlk200085589" localSheetId="0">'Reputation, Society'!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Reputation, Society'!$B$1:$M$17</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Reputation, Society'!$B$1:$L$17</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -146,7 +146,7 @@
     <numFmt numFmtId="167" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="168" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -183,12 +183,6 @@
     <font>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -802,81 +796,79 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" readingOrder="1"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -894,28 +886,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -927,14 +911,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="10" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="9" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="168" fontId="2" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -983,34 +967,34 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1045,6 +1029,11 @@
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1">
+        <row r="12">
+          <cell r="I12">
+            <v>1.4999999999999999E-2</v>
+          </cell>
+        </row>
         <row r="18">
           <cell r="V18">
             <v>0.2929459683015237</v>
@@ -1434,714 +1423,646 @@
     <tabColor rgb="FFFFFF00"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:AG23"/>
+  <dimension ref="B1:AC23"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="3.21875" style="49" customWidth="1"/>
-    <col min="3" max="3" width="37.21875" style="14" customWidth="1"/>
-    <col min="4" max="4" width="5.33203125" style="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.21875" style="31" customWidth="1"/>
-    <col min="6" max="6" width="6.88671875" style="14" customWidth="1"/>
-    <col min="7" max="7" width="6.77734375" style="14" customWidth="1"/>
-    <col min="8" max="8" width="6.21875" style="14" customWidth="1"/>
-    <col min="9" max="9" width="6.77734375" style="14" customWidth="1"/>
-    <col min="10" max="12" width="8.21875" style="14" customWidth="1"/>
-    <col min="13" max="13" width="8.21875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="6.21875" style="2" customWidth="1"/>
-    <col min="15" max="19" width="8.21875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="3.21875" style="43" customWidth="1"/>
+    <col min="3" max="3" width="37.21875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="5.33203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.21875" style="29" customWidth="1"/>
+    <col min="6" max="6" width="6.88671875" style="12" customWidth="1"/>
+    <col min="7" max="7" width="6.77734375" style="12" customWidth="1"/>
+    <col min="8" max="8" width="6.21875" style="12" customWidth="1"/>
+    <col min="9" max="9" width="6.77734375" style="12" customWidth="1"/>
+    <col min="10" max="12" width="8.21875" style="12" customWidth="1"/>
+    <col min="13" max="15" width="8.21875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:19" s="40" customFormat="1" ht="15" thickBot="1">
-      <c r="B1" s="37"/>
-      <c r="C1" s="70" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="71"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="74"/>
-      <c r="M1" s="38"/>
-      <c r="N1" s="39"/>
-      <c r="O1" s="39"/>
+    <row r="1" spans="2:15" s="36" customFormat="1" ht="15" thickBot="1">
+      <c r="B1" s="35"/>
+      <c r="C1" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="65"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="68"/>
     </row>
-    <row r="2" spans="2:19" s="46" customFormat="1" ht="25.95" customHeight="1" thickBot="1">
-      <c r="B2" s="41"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="75" t="s">
+    <row r="2" spans="2:15" s="40" customFormat="1" ht="25.95" customHeight="1" thickBot="1">
+      <c r="B2" s="37"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="78" t="s">
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="K2" s="78"/>
-      <c r="L2" s="79"/>
-      <c r="M2" s="44"/>
-      <c r="N2" s="45"/>
-      <c r="O2" s="45"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="73"/>
     </row>
-    <row r="3" spans="2:19" s="6" customFormat="1" ht="132" customHeight="1" thickBot="1">
-      <c r="B3" s="47"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="54" t="s">
+    <row r="3" spans="2:15" s="4" customFormat="1" ht="132" customHeight="1" thickBot="1">
+      <c r="B3" s="41"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="33" t="s">
+      <c r="F3" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="33" t="s">
+      <c r="G3" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="33" t="s">
+      <c r="H3" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="34" t="s">
+      <c r="I3" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="35" t="s">
+      <c r="J3" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="K3" s="36" t="s">
+      <c r="K3" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="L3" s="34" t="s">
+      <c r="L3" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
     </row>
-    <row r="4" spans="2:19" s="15" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B4" s="67" t="s">
+    <row r="4" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1">
+      <c r="B4" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="62" t="s">
+      <c r="C4" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="55">
+      <c r="D4" s="49">
         <v>3.4135987800000001</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="5">
         <v>4.9800814611259021</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="7">
         <f>[1]Sheet1!$V$18</f>
         <v>0.2929459683015237</v>
       </c>
-      <c r="H4" s="8">
-        <v>0</v>
-      </c>
-      <c r="I4" s="10" t="s">
+      <c r="H4" s="6">
+        <v>0</v>
+      </c>
+      <c r="I4" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="11">
-        <v>0</v>
-      </c>
-      <c r="K4" s="12">
-        <v>0</v>
-      </c>
-      <c r="L4" s="13">
-        <v>0</v>
-      </c>
-      <c r="M4" s="1"/>
-      <c r="N4" s="14"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="14"/>
-      <c r="Q4" s="14"/>
-      <c r="R4" s="14"/>
-      <c r="S4" s="14"/>
+      <c r="J4" s="9">
+        <v>0</v>
+      </c>
+      <c r="K4" s="10">
+        <v>0</v>
+      </c>
+      <c r="L4" s="11">
+        <v>0</v>
+      </c>
+      <c r="M4" s="12"/>
+      <c r="N4" s="12"/>
+      <c r="O4" s="12"/>
     </row>
-    <row r="5" spans="2:19" s="15" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B5" s="68"/>
-      <c r="C5" s="21" t="s">
+    <row r="5" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1">
+      <c r="B5" s="62"/>
+      <c r="C5" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="56">
+      <c r="D5" s="50">
         <v>12.720419820000002</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="5">
         <v>1.8081164242580787</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="9">
-        <v>0</v>
-      </c>
-      <c r="H5" s="8">
+      <c r="G5" s="7">
+        <v>0</v>
+      </c>
+      <c r="H5" s="6">
         <v>0.23584127272931465</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="J5" s="11">
+      <c r="J5" s="9">
         <f>[1]Sheet1!$X$21</f>
         <v>0.15722751515287642</v>
       </c>
-      <c r="K5" s="16">
+      <c r="K5" s="14">
         <f>[1]Sheet1!$X$22</f>
         <v>7.8613757576438209E-2</v>
       </c>
-      <c r="L5" s="10">
+      <c r="L5" s="8">
         <f>[1]Sheet1!$X$23</f>
         <v>0.15722751515287642</v>
       </c>
-      <c r="M5" s="1"/>
-      <c r="N5" s="14"/>
-      <c r="O5" s="14"/>
-      <c r="P5" s="14"/>
-      <c r="Q5" s="14"/>
-      <c r="R5" s="14"/>
-      <c r="S5" s="14"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="12"/>
     </row>
-    <row r="6" spans="2:19" s="15" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B6" s="68"/>
-      <c r="C6" s="21" t="s">
+    <row r="6" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1">
+      <c r="B6" s="62"/>
+      <c r="C6" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="56">
+      <c r="D6" s="50">
         <v>3.5036499999999999</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="5">
         <v>5.4229161017795731</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="9">
-        <v>0</v>
-      </c>
-      <c r="H6" s="8">
+      <c r="G6" s="7">
+        <v>0</v>
+      </c>
+      <c r="H6" s="6">
         <v>0.28541663693576702</v>
       </c>
-      <c r="I6" s="10" t="s">
+      <c r="I6" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="J6" s="11">
-        <v>0</v>
-      </c>
-      <c r="K6" s="16">
-        <v>0</v>
-      </c>
-      <c r="L6" s="10">
-        <v>0</v>
-      </c>
-      <c r="M6" s="1"/>
-      <c r="N6" s="14"/>
-      <c r="O6" s="14"/>
-      <c r="P6" s="14"/>
-      <c r="Q6" s="14"/>
-      <c r="R6" s="14"/>
-      <c r="S6" s="14"/>
+      <c r="J6" s="9">
+        <v>0</v>
+      </c>
+      <c r="K6" s="14">
+        <v>0</v>
+      </c>
+      <c r="L6" s="8">
+        <v>0</v>
+      </c>
+      <c r="M6" s="12"/>
+      <c r="N6" s="12"/>
+      <c r="O6" s="12"/>
     </row>
-    <row r="7" spans="2:19" s="15" customFormat="1" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B7" s="69"/>
-      <c r="C7" s="63" t="s">
+    <row r="7" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1" thickBot="1">
+      <c r="B7" s="63"/>
+      <c r="C7" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="57">
+      <c r="D7" s="51">
         <v>21.304912170000001</v>
       </c>
-      <c r="E7" s="7">
-        <v>0</v>
-      </c>
-      <c r="F7" s="8">
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6">
         <v>0.65712545014448642</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="7">
         <f>[1]Sheet1!$AB$18</f>
         <v>0.14081259645953281</v>
       </c>
-      <c r="H7" s="8">
-        <v>0</v>
-      </c>
-      <c r="I7" s="10" t="s">
+      <c r="H7" s="6">
+        <v>0</v>
+      </c>
+      <c r="I7" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="J7" s="17">
+      <c r="J7" s="15">
         <f>[1]Sheet1!$AB$21</f>
         <v>0.14081259645953281</v>
       </c>
-      <c r="K7" s="18">
+      <c r="K7" s="16">
         <f>[1]Sheet1!$AB$22</f>
         <v>9.3875064306355213E-2</v>
       </c>
-      <c r="L7" s="19">
+      <c r="L7" s="17">
         <f>[1]Sheet1!$AB$23</f>
         <v>4.6937532153177607E-2</v>
       </c>
-      <c r="M7" s="1"/>
-      <c r="N7" s="14"/>
-      <c r="O7" s="14"/>
-      <c r="P7" s="14"/>
-      <c r="Q7" s="14"/>
-      <c r="R7" s="14"/>
-      <c r="S7" s="14"/>
+      <c r="M7" s="12"/>
+      <c r="N7" s="12"/>
+      <c r="O7" s="12"/>
     </row>
-    <row r="8" spans="2:19" s="15" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B8" s="67" t="s">
+    <row r="8" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1">
+      <c r="B8" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="62" t="s">
+      <c r="C8" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="55">
+      <c r="D8" s="49">
         <v>7.721148311538462</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="5">
         <v>2.3312594543872254</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="6">
         <v>0.12951441413262363</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="7">
         <f>[1]Sheet1!$AD$18</f>
         <v>0.38854324239787086</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="6">
         <v>0.64757207066311817</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I8" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="J8" s="20">
+      <c r="J8" s="18">
         <f>[1]Sheet1!$AD$21</f>
         <v>0.12951441413262363</v>
       </c>
-      <c r="K8" s="12">
+      <c r="K8" s="10">
         <f>[1]Sheet1!$AD$22</f>
         <v>0.12951441413262363</v>
       </c>
-      <c r="L8" s="13">
-        <v>0</v>
-      </c>
-      <c r="M8" s="1"/>
-      <c r="N8" s="14"/>
-      <c r="O8" s="14"/>
-      <c r="P8" s="14"/>
-      <c r="Q8" s="14"/>
-      <c r="R8" s="14"/>
-      <c r="S8" s="14"/>
+      <c r="L8" s="11">
+        <v>0</v>
+      </c>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="12"/>
     </row>
-    <row r="9" spans="2:19" s="15" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B9" s="68"/>
-      <c r="C9" s="21" t="s">
+    <row r="9" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1">
+      <c r="B9" s="62"/>
+      <c r="C9" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="56">
+      <c r="D9" s="50">
         <v>12.273168915897436</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="5">
         <v>3.5035776248709567</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="6">
         <v>1.3851353400652622</v>
       </c>
-      <c r="G9" s="9">
-        <v>0</v>
-      </c>
-      <c r="H9" s="8">
+      <c r="G9" s="7">
+        <v>0</v>
+      </c>
+      <c r="H9" s="6">
         <v>0.24443564824681097</v>
       </c>
-      <c r="I9" s="10" t="s">
+      <c r="I9" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="J9" s="11">
+      <c r="J9" s="9">
         <f>[1]Sheet1!$AF$21</f>
         <v>0.32591419766241464</v>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="14">
         <f>[1]Sheet1!$AF$22</f>
         <v>0.32591419766241464</v>
       </c>
-      <c r="L9" s="10">
+      <c r="L9" s="8">
         <f>[1]Sheet1!$AF$23</f>
         <v>8.147854941560366E-2</v>
       </c>
-      <c r="M9" s="1"/>
-      <c r="N9" s="14"/>
-      <c r="O9" s="14"/>
-      <c r="P9" s="14"/>
-      <c r="Q9" s="14"/>
-      <c r="R9" s="14"/>
-      <c r="S9" s="14"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
+      <c r="O9" s="12"/>
     </row>
-    <row r="10" spans="2:19" s="15" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B10" s="68"/>
-      <c r="C10" s="21" t="s">
+    <row r="10" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1">
+      <c r="B10" s="62"/>
+      <c r="C10" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="56">
+      <c r="D10" s="50">
         <v>7.1819852465641034</v>
       </c>
-      <c r="E10" s="7">
-        <v>0</v>
-      </c>
-      <c r="F10" s="8">
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="6">
         <v>0.4177118021002918</v>
       </c>
-      <c r="G10" s="9">
-        <v>0</v>
-      </c>
-      <c r="H10" s="8">
-        <v>0</v>
-      </c>
-      <c r="I10" s="10" t="s">
+      <c r="G10" s="7">
+        <v>0</v>
+      </c>
+      <c r="H10" s="6">
+        <v>0</v>
+      </c>
+      <c r="I10" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="J10" s="11">
+      <c r="J10" s="9">
         <f>[1]Sheet1!$AH$21</f>
         <v>0.55694906946705569</v>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="14">
         <f>[1]Sheet1!$AH$22</f>
         <v>0.6961863368338197</v>
       </c>
-      <c r="L10" s="10">
-        <v>0</v>
-      </c>
-      <c r="M10" s="1"/>
-      <c r="N10" s="14"/>
-      <c r="O10" s="14"/>
-      <c r="P10" s="14"/>
-      <c r="Q10" s="14"/>
-      <c r="R10" s="14"/>
-      <c r="S10" s="14"/>
+      <c r="L10" s="8">
+        <v>0</v>
+      </c>
+      <c r="M10" s="12"/>
+      <c r="N10" s="12"/>
+      <c r="O10" s="12"/>
     </row>
-    <row r="11" spans="2:19" s="15" customFormat="1" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B11" s="69"/>
-      <c r="C11" s="63" t="s">
+    <row r="11" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1" thickBot="1">
+      <c r="B11" s="63"/>
+      <c r="C11" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="57">
+      <c r="D11" s="51">
         <v>0.57107699999999995</v>
       </c>
-      <c r="E11" s="7">
-        <v>0</v>
-      </c>
-      <c r="F11" s="8">
-        <v>0</v>
-      </c>
-      <c r="G11" s="9">
-        <v>0</v>
-      </c>
-      <c r="H11" s="8">
-        <v>0</v>
-      </c>
-      <c r="I11" s="10" t="s">
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="6">
+        <v>0</v>
+      </c>
+      <c r="G11" s="7">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6">
+        <v>0</v>
+      </c>
+      <c r="I11" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="J11" s="17">
-        <v>0</v>
-      </c>
-      <c r="K11" s="18">
-        <v>0</v>
-      </c>
-      <c r="L11" s="19">
-        <v>0</v>
-      </c>
-      <c r="M11" s="1"/>
-      <c r="N11" s="14"/>
-      <c r="O11" s="14"/>
-      <c r="P11" s="14"/>
-      <c r="Q11" s="14"/>
-      <c r="R11" s="14"/>
-      <c r="S11" s="14"/>
+      <c r="J11" s="15">
+        <v>0</v>
+      </c>
+      <c r="K11" s="16">
+        <v>0</v>
+      </c>
+      <c r="L11" s="17">
+        <v>0</v>
+      </c>
+      <c r="M11" s="12"/>
+      <c r="N11" s="12"/>
+      <c r="O11" s="12"/>
     </row>
-    <row r="12" spans="2:19" s="15" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B12" s="64" t="s">
+    <row r="12" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1">
+      <c r="B12" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="62" t="s">
+      <c r="C12" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="58">
+      <c r="D12" s="52">
         <v>1.3649733500000001</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="5">
         <v>5.128305252260053</v>
       </c>
-      <c r="F12" s="8">
-        <v>0</v>
-      </c>
-      <c r="G12" s="9">
-        <v>0</v>
-      </c>
-      <c r="H12" s="8">
-        <v>0</v>
-      </c>
-      <c r="I12" s="10" t="s">
+      <c r="F12" s="6">
+        <v>0</v>
+      </c>
+      <c r="G12" s="7">
+        <v>0</v>
+      </c>
+      <c r="H12" s="6">
+        <v>0</v>
+      </c>
+      <c r="I12" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="J12" s="20">
-        <v>0</v>
-      </c>
-      <c r="K12" s="12">
-        <v>0</v>
-      </c>
-      <c r="L12" s="13">
-        <v>0</v>
-      </c>
-      <c r="M12" s="1"/>
-      <c r="N12" s="14"/>
-      <c r="O12" s="14"/>
-      <c r="P12" s="14"/>
-      <c r="Q12" s="14"/>
-      <c r="R12" s="14"/>
-      <c r="S12" s="14"/>
+      <c r="J12" s="18">
+        <v>0</v>
+      </c>
+      <c r="K12" s="10">
+        <v>0</v>
+      </c>
+      <c r="L12" s="11">
+        <v>0</v>
+      </c>
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="12"/>
     </row>
-    <row r="13" spans="2:19" s="15" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B13" s="65"/>
-      <c r="C13" s="21" t="s">
+    <row r="13" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1">
+      <c r="B13" s="59"/>
+      <c r="C13" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="59">
+      <c r="D13" s="53">
         <v>7.5363555180000006</v>
       </c>
-      <c r="E13" s="7">
-        <v>0</v>
-      </c>
-      <c r="F13" s="8">
-        <v>0</v>
-      </c>
-      <c r="G13" s="9">
-        <v>0</v>
-      </c>
-      <c r="H13" s="8">
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="6">
+        <v>0</v>
+      </c>
+      <c r="G13" s="7">
+        <v>0</v>
+      </c>
+      <c r="H13" s="6">
         <v>0.39807039262342825</v>
       </c>
-      <c r="I13" s="10" t="s">
+      <c r="I13" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="J13" s="11">
-        <v>0</v>
-      </c>
-      <c r="K13" s="16">
-        <v>0</v>
-      </c>
-      <c r="L13" s="10">
-        <v>0</v>
-      </c>
-      <c r="M13" s="1"/>
-      <c r="N13" s="14"/>
-      <c r="O13" s="14"/>
-      <c r="P13" s="14"/>
-      <c r="Q13" s="14"/>
-      <c r="R13" s="14"/>
-      <c r="S13" s="14"/>
+      <c r="J13" s="9">
+        <v>0</v>
+      </c>
+      <c r="K13" s="14">
+        <v>0</v>
+      </c>
+      <c r="L13" s="8">
+        <v>0</v>
+      </c>
+      <c r="M13" s="12"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="12"/>
     </row>
-    <row r="14" spans="2:19" s="15" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B14" s="65"/>
-      <c r="C14" s="21" t="s">
+    <row r="14" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1">
+      <c r="B14" s="59"/>
+      <c r="C14" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="59">
+      <c r="D14" s="53">
         <v>2.1255060000000001</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="5">
         <v>2.8228572396408196</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="6">
         <v>1.4114286198204098</v>
       </c>
-      <c r="G14" s="9">
-        <v>0</v>
-      </c>
-      <c r="H14" s="8">
+      <c r="G14" s="7">
+        <v>0</v>
+      </c>
+      <c r="H14" s="6">
         <v>1.4114286198204098</v>
       </c>
-      <c r="I14" s="10" t="s">
+      <c r="I14" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="J14" s="11">
-        <v>0</v>
-      </c>
-      <c r="K14" s="16">
-        <v>0</v>
-      </c>
-      <c r="L14" s="10">
-        <v>0</v>
-      </c>
-      <c r="M14" s="1"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="14"/>
-      <c r="P14" s="14"/>
-      <c r="Q14" s="14"/>
-      <c r="R14" s="14"/>
-      <c r="S14" s="14"/>
+      <c r="J14" s="9">
+        <v>0</v>
+      </c>
+      <c r="K14" s="14">
+        <v>0</v>
+      </c>
+      <c r="L14" s="8">
+        <v>0</v>
+      </c>
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="12"/>
     </row>
-    <row r="15" spans="2:19" s="15" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B15" s="65"/>
-      <c r="C15" s="21" t="s">
+    <row r="15" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1">
+      <c r="B15" s="59"/>
+      <c r="C15" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="59">
+      <c r="D15" s="53">
         <v>1.4569589599999999</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="5">
         <v>4.8045279188921013</v>
       </c>
-      <c r="F15" s="8">
-        <v>0</v>
-      </c>
-      <c r="G15" s="9">
-        <v>0</v>
-      </c>
-      <c r="H15" s="8">
-        <v>0</v>
-      </c>
-      <c r="I15" s="10" t="s">
+      <c r="F15" s="6">
+        <v>0</v>
+      </c>
+      <c r="G15" s="7">
+        <v>0</v>
+      </c>
+      <c r="H15" s="6">
+        <v>0</v>
+      </c>
+      <c r="I15" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="J15" s="11">
-        <v>0</v>
-      </c>
-      <c r="K15" s="16">
-        <v>0</v>
-      </c>
-      <c r="L15" s="10">
-        <v>0</v>
-      </c>
-      <c r="M15" s="1"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="14"/>
-      <c r="P15" s="14"/>
-      <c r="Q15" s="14"/>
-      <c r="R15" s="14"/>
-      <c r="S15" s="14"/>
+      <c r="J15" s="9">
+        <v>0</v>
+      </c>
+      <c r="K15" s="14">
+        <v>0</v>
+      </c>
+      <c r="L15" s="8">
+        <v>0</v>
+      </c>
+      <c r="M15" s="12"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="12"/>
     </row>
-    <row r="16" spans="2:19" s="15" customFormat="1" ht="15.45" customHeight="1" thickBot="1">
-      <c r="B16" s="66"/>
-      <c r="C16" s="63" t="s">
+    <row r="16" spans="2:15" s="13" customFormat="1" ht="15.45" customHeight="1" thickBot="1">
+      <c r="B16" s="60"/>
+      <c r="C16" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="60">
+      <c r="D16" s="54">
         <v>5.7995670199999996</v>
       </c>
-      <c r="E16" s="22">
-        <v>0</v>
-      </c>
-      <c r="F16" s="23">
-        <v>0</v>
-      </c>
-      <c r="G16" s="24">
+      <c r="E16" s="20">
+        <v>0</v>
+      </c>
+      <c r="F16" s="21">
+        <v>0</v>
+      </c>
+      <c r="G16" s="22">
         <f>[1]Sheet1!$AT$18</f>
         <v>0.17242666505128171</v>
       </c>
-      <c r="H16" s="23">
-        <v>0</v>
-      </c>
-      <c r="I16" s="10" t="s">
+      <c r="H16" s="21">
+        <v>0</v>
+      </c>
+      <c r="I16" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="J16" s="17">
+      <c r="J16" s="15">
         <f>[1]Sheet1!$AT$21</f>
         <v>0.17242666505128171</v>
       </c>
-      <c r="K16" s="18">
-        <v>0</v>
-      </c>
-      <c r="L16" s="19">
-        <v>0</v>
-      </c>
-      <c r="M16" s="1"/>
-      <c r="N16" s="14"/>
-      <c r="O16" s="14"/>
-      <c r="P16" s="14"/>
-      <c r="Q16" s="14"/>
-      <c r="R16" s="14"/>
-      <c r="S16" s="14"/>
+      <c r="K16" s="16">
+        <v>0</v>
+      </c>
+      <c r="L16" s="17">
+        <v>0</v>
+      </c>
+      <c r="M16" s="12"/>
+      <c r="N16" s="12"/>
+      <c r="O16" s="12"/>
     </row>
-    <row r="17" spans="2:33" s="27" customFormat="1">
-      <c r="B17" s="48"/>
-      <c r="C17" s="50" t="s">
+    <row r="17" spans="2:29" s="25" customFormat="1">
+      <c r="B17" s="42"/>
+      <c r="C17" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="61">
+      <c r="D17" s="55">
         <v>86.97332109200002</v>
       </c>
-      <c r="E17" s="51">
+      <c r="E17" s="45">
         <v>0.3449333614415635</v>
       </c>
-      <c r="F17" s="51">
+      <c r="F17" s="45">
         <v>0.3449333614415635</v>
       </c>
-      <c r="G17" s="51">
+      <c r="G17" s="45">
         <v>0.3449333614415635</v>
       </c>
-      <c r="H17" s="51">
+      <c r="H17" s="45">
         <v>0.3449333614415635</v>
       </c>
-      <c r="I17" s="52" t="s">
+      <c r="I17" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="J17" s="53">
+      <c r="J17" s="47">
         <v>2.8744446786796956E-3</v>
       </c>
-      <c r="K17" s="53">
+      <c r="K17" s="47">
         <v>2.8744446786796956E-3</v>
       </c>
-      <c r="L17" s="53">
+      <c r="L17" s="47">
         <v>2.8744446786796956E-3</v>
       </c>
-      <c r="M17" s="26"/>
-      <c r="N17" s="26"/>
-      <c r="O17" s="26"/>
-      <c r="P17" s="26"/>
-      <c r="Q17" s="26"/>
-      <c r="R17" s="26"/>
-      <c r="S17" s="26"/>
-      <c r="T17" s="26"/>
-      <c r="U17" s="26"/>
-      <c r="V17" s="26"/>
-      <c r="W17" s="26"/>
-      <c r="X17" s="26"/>
-      <c r="Y17" s="26"/>
-      <c r="Z17" s="26"/>
-      <c r="AA17" s="26"/>
-      <c r="AB17" s="26"/>
-      <c r="AC17" s="26"/>
-      <c r="AD17" s="26"/>
-      <c r="AE17" s="26"/>
-      <c r="AF17" s="26"/>
-      <c r="AG17" s="26"/>
+      <c r="M17" s="24"/>
+      <c r="N17" s="24"/>
+      <c r="O17" s="24"/>
+      <c r="P17" s="24"/>
+      <c r="Q17" s="24"/>
+      <c r="R17" s="24"/>
+      <c r="S17" s="24"/>
+      <c r="T17" s="24"/>
+      <c r="U17" s="24"/>
+      <c r="V17" s="24"/>
+      <c r="W17" s="24"/>
+      <c r="X17" s="24"/>
+      <c r="Y17" s="24"/>
+      <c r="Z17" s="24"/>
+      <c r="AA17" s="24"/>
+      <c r="AB17" s="24"/>
+      <c r="AC17" s="24"/>
     </row>
-    <row r="19" spans="2:33" ht="14.55" hidden="1" customHeight="1">
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="30"/>
+    <row r="19" spans="2:29" ht="14.55" hidden="1" customHeight="1">
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="28"/>
     </row>
-    <row r="20" spans="2:33" ht="14.55" hidden="1" customHeight="1">
-      <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="28"/>
+    <row r="20" spans="2:29" ht="14.55" hidden="1" customHeight="1">
+      <c r="C20" s="23"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="26"/>
     </row>
-    <row r="21" spans="2:33" ht="14.55" hidden="1" customHeight="1">
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28"/>
+    <row r="21" spans="2:29" ht="14.55" hidden="1" customHeight="1">
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
     </row>
-    <row r="22" spans="2:33" ht="14.55" hidden="1" customHeight="1"/>
-    <row r="23" spans="2:33" ht="14.55" hidden="1" customHeight="1"/>
+    <row r="22" spans="2:29" ht="14.55" hidden="1" customHeight="1"/>
+    <row r="23" spans="2:29" ht="14.55" hidden="1" customHeight="1"/>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="B12:B16"/>

--- a/data/Heat map 7.xlsx
+++ b/data/Heat map 7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74E36548-B354-4D67-A62E-93A33D3D59F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50FD7568-D23D-4263-B5F8-08671374E425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{462AB6D2-C8E4-47A1-AF79-F15809A5475A}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{462AB6D2-C8E4-47A1-AF79-F15809A5475A}"/>
   </bookViews>
   <sheets>
     <sheet name="Reputation, Society" sheetId="1" r:id="rId1"/>
@@ -54,9 +54,6 @@
     <t>Society Impact &amp; Inclusion</t>
   </si>
   <si>
-    <t>GI</t>
-  </si>
-  <si>
     <t>Biotech</t>
   </si>
   <si>
@@ -72,9 +69,6 @@
     <t>Seed System</t>
   </si>
   <si>
-    <t>RAFS</t>
-  </si>
-  <si>
     <t>Plant Health</t>
   </si>
   <si>
@@ -84,9 +78,6 @@
     <t>Mechanization</t>
   </si>
   <si>
-    <t>ST</t>
-  </si>
-  <si>
     <t>per Program Target (target/13)</t>
   </si>
   <si>
@@ -133,6 +124,15 @@
   </si>
   <si>
     <t>Value Chain Markets and Agribusiness</t>
+  </si>
+  <si>
+    <t>Genetic Innovation</t>
+  </si>
+  <si>
+    <t>Resilient Agrifood Systems</t>
+  </si>
+  <si>
+    <t>Systems Transformation</t>
   </si>
 </sst>
 </file>
@@ -1474,31 +1474,31 @@
       <c r="B3" s="41"/>
       <c r="C3" s="2"/>
       <c r="D3" s="48" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E3" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="31" t="s">
+      <c r="I3" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="31" t="s">
+      <c r="J3" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="31" t="s">
+      <c r="K3" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="32" t="s">
+      <c r="L3" s="32" t="s">
         <v>19</v>
-      </c>
-      <c r="J3" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3" s="32" t="s">
-        <v>22</v>
       </c>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
@@ -1506,10 +1506,10 @@
     </row>
     <row r="4" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1">
       <c r="B4" s="61" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="56" t="s">
         <v>3</v>
-      </c>
-      <c r="C4" s="56" t="s">
-        <v>4</v>
       </c>
       <c r="D4" s="49">
         <v>3.4135987800000001</v>
@@ -1518,7 +1518,7 @@
         <v>4.9800814611259021</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G4" s="7">
         <f>[1]Sheet1!$V$18</f>
@@ -1528,7 +1528,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J4" s="9">
         <v>0</v>
@@ -1546,7 +1546,7 @@
     <row r="5" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1">
       <c r="B5" s="62"/>
       <c r="C5" s="19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" s="50">
         <v>12.720419820000002</v>
@@ -1555,7 +1555,7 @@
         <v>1.8081164242580787</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5" s="7">
         <v>0</v>
@@ -1564,7 +1564,7 @@
         <v>0.23584127272931465</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J5" s="9">
         <f>[1]Sheet1!$X$21</f>
@@ -1585,7 +1585,7 @@
     <row r="6" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1">
       <c r="B6" s="62"/>
       <c r="C6" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D6" s="50">
         <v>3.5036499999999999</v>
@@ -1594,7 +1594,7 @@
         <v>5.4229161017795731</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6" s="7">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>0.28541663693576702</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J6" s="9">
         <v>0</v>
@@ -1621,7 +1621,7 @@
     <row r="7" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1" thickBot="1">
       <c r="B7" s="63"/>
       <c r="C7" s="57" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D7" s="51">
         <v>21.304912170000001</v>
@@ -1640,7 +1640,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J7" s="15">
         <f>[1]Sheet1!$AB$21</f>
@@ -1660,10 +1660,10 @@
     </row>
     <row r="8" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1">
       <c r="B8" s="61" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C8" s="56" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D8" s="49">
         <v>7.721148311538462</v>
@@ -1682,7 +1682,7 @@
         <v>0.64757207066311817</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J8" s="18">
         <f>[1]Sheet1!$AD$21</f>
@@ -1702,7 +1702,7 @@
     <row r="9" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1">
       <c r="B9" s="62"/>
       <c r="C9" s="19" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D9" s="50">
         <v>12.273168915897436</v>
@@ -1720,7 +1720,7 @@
         <v>0.24443564824681097</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J9" s="9">
         <f>[1]Sheet1!$AF$21</f>
@@ -1741,7 +1741,7 @@
     <row r="10" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1">
       <c r="B10" s="62"/>
       <c r="C10" s="19" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D10" s="50">
         <v>7.1819852465641034</v>
@@ -1759,7 +1759,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J10" s="9">
         <f>[1]Sheet1!$AH$21</f>
@@ -1779,7 +1779,7 @@
     <row r="11" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1" thickBot="1">
       <c r="B11" s="63"/>
       <c r="C11" s="57" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D11" s="51">
         <v>0.57107699999999995</v>
@@ -1797,7 +1797,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J11" s="15">
         <v>0</v>
@@ -1814,10 +1814,10 @@
     </row>
     <row r="12" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1">
       <c r="B12" s="58" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C12" s="56" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D12" s="52">
         <v>1.3649733500000001</v>
@@ -1835,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J12" s="18">
         <v>0</v>
@@ -1853,7 +1853,7 @@
     <row r="13" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1">
       <c r="B13" s="59"/>
       <c r="C13" s="19" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D13" s="53">
         <v>7.5363555180000006</v>
@@ -1871,7 +1871,7 @@
         <v>0.39807039262342825</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J13" s="9">
         <v>0</v>
@@ -1889,7 +1889,7 @@
     <row r="14" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1">
       <c r="B14" s="59"/>
       <c r="C14" s="19" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D14" s="53">
         <v>2.1255060000000001</v>
@@ -1907,7 +1907,7 @@
         <v>1.4114286198204098</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J14" s="9">
         <v>0</v>
@@ -1925,7 +1925,7 @@
     <row r="15" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1">
       <c r="B15" s="59"/>
       <c r="C15" s="19" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D15" s="53">
         <v>1.4569589599999999</v>
@@ -1943,7 +1943,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J15" s="9">
         <v>0</v>
@@ -1961,7 +1961,7 @@
     <row r="16" spans="2:15" s="13" customFormat="1" ht="15.45" customHeight="1" thickBot="1">
       <c r="B16" s="60"/>
       <c r="C16" s="57" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D16" s="54">
         <v>5.7995670199999996</v>
@@ -1980,7 +1980,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J16" s="15">
         <f>[1]Sheet1!$AT$21</f>
@@ -1999,7 +1999,7 @@
     <row r="17" spans="2:29" s="25" customFormat="1">
       <c r="B17" s="42"/>
       <c r="C17" s="44" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D17" s="55">
         <v>86.97332109200002</v>
@@ -2017,7 +2017,7 @@
         <v>0.3449333614415635</v>
       </c>
       <c r="I17" s="46" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J17" s="47">
         <v>2.8744446786796956E-3</v>

--- a/data/Heat map 7.xlsx
+++ b/data/Heat map 7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50FD7568-D23D-4263-B5F8-08671374E425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A666669B-5979-4079-8951-3769504A86D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{462AB6D2-C8E4-47A1-AF79-F15809A5475A}"/>
+    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="9960" xr2:uid="{462AB6D2-C8E4-47A1-AF79-F15809A5475A}"/>
   </bookViews>
   <sheets>
     <sheet name="Reputation, Society" sheetId="1" r:id="rId1"/>
@@ -105,9 +105,6 @@
     <t>Approved proposals with nutrition ad health components</t>
   </si>
   <si>
-    <t>USD</t>
-  </si>
-  <si>
     <t>Natural Resource Management</t>
   </si>
   <si>
@@ -133,6 +130,9 @@
   </si>
   <si>
     <t>Systems Transformation</t>
+  </si>
+  <si>
+    <t>USD (million)</t>
   </si>
 </sst>
 </file>
@@ -796,7 +796,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -920,9 +920,6 @@
     <xf numFmtId="165" fontId="13" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="167" fontId="9" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1440,41 +1437,41 @@
   <sheetData>
     <row r="1" spans="2:15" s="36" customFormat="1" ht="15" thickBot="1">
       <c r="B1" s="35"/>
-      <c r="C1" s="64" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="65"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="68"/>
+      <c r="C1" s="63" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="64"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="66"/>
+      <c r="L1" s="67"/>
     </row>
     <row r="2" spans="2:15" s="40" customFormat="1" ht="25.95" customHeight="1" thickBot="1">
       <c r="B2" s="37"/>
       <c r="C2" s="38"/>
       <c r="D2" s="39"/>
-      <c r="E2" s="69" t="s">
+      <c r="E2" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="72" t="s">
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="K2" s="72"/>
-      <c r="L2" s="73"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="72"/>
     </row>
     <row r="3" spans="2:15" s="4" customFormat="1" ht="132" customHeight="1" thickBot="1">
       <c r="B3" s="41"/>
       <c r="C3" s="2"/>
-      <c r="D3" s="48" t="s">
-        <v>20</v>
+      <c r="D3" s="30" t="s">
+        <v>29</v>
       </c>
       <c r="E3" s="30" t="s">
         <v>12</v>
@@ -1505,13 +1502,13 @@
       <c r="O3" s="3"/>
     </row>
     <row r="4" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B4" s="61" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="56" t="s">
+      <c r="B4" s="60" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="49">
+      <c r="D4" s="48">
         <v>3.4135987800000001</v>
       </c>
       <c r="E4" s="5">
@@ -1544,11 +1541,11 @@
       <c r="O4" s="12"/>
     </row>
     <row r="5" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B5" s="62"/>
+      <c r="B5" s="61"/>
       <c r="C5" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="50">
+      <c r="D5" s="49">
         <v>12.720419820000002</v>
       </c>
       <c r="E5" s="5">
@@ -1583,11 +1580,11 @@
       <c r="O5" s="12"/>
     </row>
     <row r="6" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B6" s="62"/>
+      <c r="B6" s="61"/>
       <c r="C6" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="50">
+      <c r="D6" s="49">
         <v>3.5036499999999999</v>
       </c>
       <c r="E6" s="5">
@@ -1619,11 +1616,11 @@
       <c r="O6" s="12"/>
     </row>
     <row r="7" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B7" s="63"/>
-      <c r="C7" s="57" t="s">
+      <c r="B7" s="62"/>
+      <c r="C7" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="51">
+      <c r="D7" s="50">
         <v>21.304912170000001</v>
       </c>
       <c r="E7" s="5">
@@ -1659,13 +1656,13 @@
       <c r="O7" s="12"/>
     </row>
     <row r="8" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B8" s="61" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="56" t="s">
+      <c r="B8" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="49">
+      <c r="D8" s="48">
         <v>7.721148311538462</v>
       </c>
       <c r="E8" s="5">
@@ -1700,11 +1697,11 @@
       <c r="O8" s="12"/>
     </row>
     <row r="9" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B9" s="62"/>
+      <c r="B9" s="61"/>
       <c r="C9" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="50">
+      <c r="D9" s="49">
         <v>12.273168915897436</v>
       </c>
       <c r="E9" s="5">
@@ -1739,11 +1736,11 @@
       <c r="O9" s="12"/>
     </row>
     <row r="10" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B10" s="62"/>
+      <c r="B10" s="61"/>
       <c r="C10" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="50">
+        <v>20</v>
+      </c>
+      <c r="D10" s="49">
         <v>7.1819852465641034</v>
       </c>
       <c r="E10" s="5">
@@ -1777,11 +1774,11 @@
       <c r="O10" s="12"/>
     </row>
     <row r="11" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B11" s="63"/>
-      <c r="C11" s="57" t="s">
+      <c r="B11" s="62"/>
+      <c r="C11" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="51">
+      <c r="D11" s="50">
         <v>0.57107699999999995</v>
       </c>
       <c r="E11" s="5">
@@ -1813,13 +1810,13 @@
       <c r="O11" s="12"/>
     </row>
     <row r="12" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B12" s="58" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="56" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="52">
+      <c r="B12" s="57" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="51">
         <v>1.3649733500000001</v>
       </c>
       <c r="E12" s="5">
@@ -1851,11 +1848,11 @@
       <c r="O12" s="12"/>
     </row>
     <row r="13" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B13" s="59"/>
+      <c r="B13" s="58"/>
       <c r="C13" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="53">
+        <v>22</v>
+      </c>
+      <c r="D13" s="52">
         <v>7.5363555180000006</v>
       </c>
       <c r="E13" s="5">
@@ -1887,11 +1884,11 @@
       <c r="O13" s="12"/>
     </row>
     <row r="14" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B14" s="59"/>
+      <c r="B14" s="58"/>
       <c r="C14" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="53">
+        <v>23</v>
+      </c>
+      <c r="D14" s="52">
         <v>2.1255060000000001</v>
       </c>
       <c r="E14" s="5">
@@ -1923,11 +1920,11 @@
       <c r="O14" s="12"/>
     </row>
     <row r="15" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B15" s="59"/>
+      <c r="B15" s="58"/>
       <c r="C15" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="53">
+        <v>24</v>
+      </c>
+      <c r="D15" s="52">
         <v>1.4569589599999999</v>
       </c>
       <c r="E15" s="5">
@@ -1959,11 +1956,11 @@
       <c r="O15" s="12"/>
     </row>
     <row r="16" spans="2:15" s="13" customFormat="1" ht="15.45" customHeight="1" thickBot="1">
-      <c r="B16" s="60"/>
-      <c r="C16" s="57" t="s">
-        <v>26</v>
-      </c>
-      <c r="D16" s="54">
+      <c r="B16" s="59"/>
+      <c r="C16" s="56" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="53">
         <v>5.7995670199999996</v>
       </c>
       <c r="E16" s="20">
@@ -2001,7 +1998,7 @@
       <c r="C17" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="55">
+      <c r="D17" s="54">
         <v>86.97332109200002</v>
       </c>
       <c r="E17" s="45">

--- a/data/Heat map 7.xlsx
+++ b/data/Heat map 7.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A666669B-5979-4079-8951-3769504A86D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B2A7F99-962C-44E6-B295-9242338B7068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="9960" xr2:uid="{462AB6D2-C8E4-47A1-AF79-F15809A5475A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{462AB6D2-C8E4-47A1-AF79-F15809A5475A}"/>
   </bookViews>
   <sheets>
     <sheet name="Reputation, Society" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </externalReferences>
   <definedNames>
     <definedName name="_Hlk200085589" localSheetId="0">'Reputation, Society'!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Reputation, Society'!$B$1:$L$17</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Reputation, Society'!$A$1:$K$17</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>KPI by $</t>
   </si>
@@ -54,12 +54,6 @@
     <t>Society Impact &amp; Inclusion</t>
   </si>
   <si>
-    <t>Biotech</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Breeding</t>
   </si>
   <si>
@@ -132,7 +126,14 @@
     <t>Systems Transformation</t>
   </si>
   <si>
-    <t>USD (million)</t>
+    <t>USD
+ (million)</t>
+  </si>
+  <si>
+    <t>Biotechnology</t>
+  </si>
+  <si>
+    <t>IITA Program</t>
   </si>
 </sst>
 </file>
@@ -146,7 +147,7 @@
     <numFmt numFmtId="167" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="168" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -266,7 +267,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="41">
+  <borders count="43">
     <border>
       <left/>
       <right/>
@@ -454,17 +455,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -583,21 +573,6 @@
     </border>
     <border>
       <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
         <color indexed="64"/>
       </left>
       <right/>
@@ -662,37 +637,6 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top/>
       <bottom/>
       <diagonal/>
@@ -762,13 +706,28 @@
     </border>
     <border>
       <left style="medium">
-        <color theme="1"/>
+        <color indexed="64"/>
       </left>
       <right style="medium">
-        <color theme="1"/>
+        <color indexed="64"/>
       </right>
       <top style="medium">
-        <color theme="1"/>
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
         <color indexed="64"/>
@@ -777,16 +736,90 @@
     </border>
     <border>
       <left style="medium">
-        <color theme="1"/>
+        <color indexed="64"/>
       </left>
       <right style="medium">
-        <color theme="1"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
-        <color theme="1"/>
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -796,12 +829,9 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" readingOrder="1"/>
-    </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -816,10 +846,7 @@
     <xf numFmtId="166" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -827,31 +854,22 @@
     </xf>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="19" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -871,128 +889,155 @@
     <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="42" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="9" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="9" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1420,673 +1465,680 @@
     <tabColor rgb="FFFFFF00"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:AC23"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:AB23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="3.21875" style="43" customWidth="1"/>
-    <col min="3" max="3" width="37.21875" style="12" customWidth="1"/>
-    <col min="4" max="4" width="5.33203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.21875" style="29" customWidth="1"/>
-    <col min="6" max="6" width="6.88671875" style="12" customWidth="1"/>
-    <col min="7" max="7" width="6.77734375" style="12" customWidth="1"/>
-    <col min="8" max="8" width="6.21875" style="12" customWidth="1"/>
-    <col min="9" max="9" width="6.77734375" style="12" customWidth="1"/>
-    <col min="10" max="12" width="8.21875" style="12" customWidth="1"/>
-    <col min="13" max="15" width="8.21875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" style="28" customWidth="1"/>
+    <col min="2" max="2" width="37.21875" style="10" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.21875" style="24" customWidth="1"/>
+    <col min="5" max="5" width="6.88671875" style="10" customWidth="1"/>
+    <col min="6" max="6" width="6.77734375" style="10" customWidth="1"/>
+    <col min="7" max="7" width="6.21875" style="10" customWidth="1"/>
+    <col min="8" max="8" width="6.77734375" style="10" customWidth="1"/>
+    <col min="9" max="11" width="8.21875" style="10" customWidth="1"/>
+    <col min="12" max="14" width="8.21875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" s="36" customFormat="1" ht="15" thickBot="1">
-      <c r="B1" s="35"/>
-      <c r="C1" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="64"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="66"/>
-      <c r="L1" s="67"/>
+    <row r="1" spans="1:14" s="27" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="26"/>
+      <c r="B1" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="42"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="45"/>
     </row>
-    <row r="2" spans="2:15" s="40" customFormat="1" ht="25.95" customHeight="1" thickBot="1">
-      <c r="B2" s="37"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="68" t="s">
+    <row r="2" spans="1:14" s="61" customFormat="1" ht="25.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="52"/>
+      <c r="B2" s="54" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="71" t="s">
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="K2" s="71"/>
-      <c r="L2" s="72"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="60"/>
     </row>
-    <row r="3" spans="2:15" s="4" customFormat="1" ht="132" customHeight="1" thickBot="1">
-      <c r="B3" s="41"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" s="30" t="s">
+    <row r="3" spans="1:14" s="3" customFormat="1" ht="132" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="53"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="69" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="69" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="31" t="s">
+      <c r="G3" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="31" t="s">
+      <c r="H3" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="31" t="s">
+      <c r="I3" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="32" t="s">
+      <c r="J3" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="33" t="s">
+      <c r="K3" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
     </row>
-    <row r="4" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B4" s="60" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="55" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="48">
+    <row r="4" spans="1:14" s="11" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="47" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="29">
         <v>3.4135987800000001</v>
       </c>
-      <c r="E4" s="5">
+      <c r="D4" s="62">
         <v>4.9800814611259021</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4" s="7">
+      <c r="E4" s="63">
+        <v>0</v>
+      </c>
+      <c r="F4" s="64">
         <f>[1]Sheet1!$V$18</f>
         <v>0.2929459683015237</v>
       </c>
-      <c r="H4" s="6">
-        <v>0</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="J4" s="9">
-        <v>0</v>
-      </c>
-      <c r="K4" s="10">
-        <v>0</v>
-      </c>
-      <c r="L4" s="11">
-        <v>0</v>
-      </c>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12"/>
-      <c r="O4" s="12"/>
+      <c r="G4" s="65">
+        <v>0</v>
+      </c>
+      <c r="H4" s="9">
+        <v>0</v>
+      </c>
+      <c r="I4" s="66">
+        <v>0</v>
+      </c>
+      <c r="J4" s="8">
+        <v>0</v>
+      </c>
+      <c r="K4" s="9">
+        <v>0</v>
+      </c>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
     </row>
-    <row r="5" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B5" s="61"/>
-      <c r="C5" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="49">
+    <row r="5" spans="1:14" s="11" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="39"/>
+      <c r="B5" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="30">
         <v>12.720419820000002</v>
       </c>
-      <c r="E5" s="5">
+      <c r="D5" s="4">
         <v>1.8081164242580787</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="G5" s="7">
-        <v>0</v>
-      </c>
-      <c r="H5" s="6">
+      <c r="E5" s="16">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
         <v>0.23584127272931465</v>
       </c>
-      <c r="I5" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="J5" s="9">
+      <c r="H5" s="7">
+        <v>0</v>
+      </c>
+      <c r="I5" s="67">
         <f>[1]Sheet1!$X$21</f>
         <v>0.15722751515287642</v>
       </c>
-      <c r="K5" s="14">
+      <c r="J5" s="12">
         <f>[1]Sheet1!$X$22</f>
         <v>7.8613757576438209E-2</v>
       </c>
-      <c r="L5" s="8">
+      <c r="K5" s="7">
         <f>[1]Sheet1!$X$23</f>
         <v>0.15722751515287642</v>
       </c>
-      <c r="M5" s="12"/>
-      <c r="N5" s="12"/>
-      <c r="O5" s="12"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
     </row>
-    <row r="6" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B6" s="61"/>
-      <c r="C6" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="49">
+    <row r="6" spans="1:14" s="11" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="39"/>
+      <c r="B6" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="30">
         <v>3.5036499999999999</v>
       </c>
-      <c r="E6" s="5">
+      <c r="D6" s="4">
         <v>5.4229161017795731</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="G6" s="7">
-        <v>0</v>
-      </c>
-      <c r="H6" s="6">
+      <c r="E6" s="16">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5">
         <v>0.28541663693576702</v>
       </c>
-      <c r="I6" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="J6" s="9">
-        <v>0</v>
-      </c>
-      <c r="K6" s="14">
-        <v>0</v>
-      </c>
-      <c r="L6" s="8">
-        <v>0</v>
-      </c>
-      <c r="M6" s="12"/>
-      <c r="N6" s="12"/>
-      <c r="O6" s="12"/>
+      <c r="H6" s="7">
+        <v>0</v>
+      </c>
+      <c r="I6" s="67">
+        <v>0</v>
+      </c>
+      <c r="J6" s="12">
+        <v>0</v>
+      </c>
+      <c r="K6" s="7">
+        <v>0</v>
+      </c>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
     </row>
-    <row r="7" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B7" s="62"/>
-      <c r="C7" s="56" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="50">
+    <row r="7" spans="1:14" s="11" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="40"/>
+      <c r="B7" s="49" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="31">
         <v>21.304912170000001</v>
       </c>
-      <c r="E7" s="5">
-        <v>0</v>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="16">
+        <v>0.65712545014448642</v>
       </c>
       <c r="F7" s="6">
-        <v>0.65712545014448642</v>
-      </c>
-      <c r="G7" s="7">
         <f>[1]Sheet1!$AB$18</f>
         <v>0.14081259645953281</v>
       </c>
-      <c r="H7" s="6">
-        <v>0</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="J7" s="15">
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="7">
+        <v>0</v>
+      </c>
+      <c r="I7" s="68">
         <f>[1]Sheet1!$AB$21</f>
         <v>0.14081259645953281</v>
       </c>
-      <c r="K7" s="16">
+      <c r="J7" s="13">
         <f>[1]Sheet1!$AB$22</f>
         <v>9.3875064306355213E-2</v>
       </c>
-      <c r="L7" s="17">
+      <c r="K7" s="14">
         <f>[1]Sheet1!$AB$23</f>
         <v>4.6937532153177607E-2</v>
       </c>
-      <c r="M7" s="12"/>
-      <c r="N7" s="12"/>
-      <c r="O7" s="12"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
     </row>
-    <row r="8" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B8" s="60" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="55" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="48">
+    <row r="8" spans="1:14" s="11" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="47" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="29">
         <v>7.721148311538462</v>
       </c>
-      <c r="E8" s="5">
+      <c r="D8" s="4">
         <v>2.3312594543872254</v>
       </c>
+      <c r="E8" s="16">
+        <v>0.12951441413262363</v>
+      </c>
       <c r="F8" s="6">
-        <v>0.12951441413262363</v>
-      </c>
-      <c r="G8" s="7">
         <f>[1]Sheet1!$AD$18</f>
         <v>0.38854324239787086</v>
       </c>
-      <c r="H8" s="6">
+      <c r="G8" s="5">
         <v>0.64757207066311817</v>
       </c>
-      <c r="I8" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="J8" s="18">
+      <c r="H8" s="7">
+        <v>0</v>
+      </c>
+      <c r="I8" s="66">
         <f>[1]Sheet1!$AD$21</f>
         <v>0.12951441413262363</v>
       </c>
-      <c r="K8" s="10">
+      <c r="J8" s="8">
         <f>[1]Sheet1!$AD$22</f>
         <v>0.12951441413262363</v>
       </c>
-      <c r="L8" s="11">
-        <v>0</v>
-      </c>
-      <c r="M8" s="12"/>
-      <c r="N8" s="12"/>
-      <c r="O8" s="12"/>
+      <c r="K8" s="9">
+        <v>0</v>
+      </c>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
     </row>
-    <row r="9" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B9" s="61"/>
-      <c r="C9" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="49">
+    <row r="9" spans="1:14" s="11" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="39"/>
+      <c r="B9" s="48" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="30">
         <v>12.273168915897436</v>
       </c>
-      <c r="E9" s="5">
+      <c r="D9" s="4">
         <v>3.5035776248709567</v>
       </c>
+      <c r="E9" s="16">
+        <v>1.3851353400652622</v>
+      </c>
       <c r="F9" s="6">
-        <v>1.3851353400652622</v>
-      </c>
-      <c r="G9" s="7">
-        <v>0</v>
-      </c>
-      <c r="H9" s="6">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5">
         <v>0.24443564824681097</v>
       </c>
-      <c r="I9" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="J9" s="9">
+      <c r="H9" s="7">
+        <v>0</v>
+      </c>
+      <c r="I9" s="67">
         <f>[1]Sheet1!$AF$21</f>
         <v>0.32591419766241464</v>
       </c>
-      <c r="K9" s="14">
+      <c r="J9" s="12">
         <f>[1]Sheet1!$AF$22</f>
         <v>0.32591419766241464</v>
       </c>
-      <c r="L9" s="8">
+      <c r="K9" s="7">
         <f>[1]Sheet1!$AF$23</f>
         <v>8.147854941560366E-2</v>
       </c>
-      <c r="M9" s="12"/>
-      <c r="N9" s="12"/>
-      <c r="O9" s="12"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
     </row>
-    <row r="10" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B10" s="61"/>
-      <c r="C10" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="49">
+    <row r="10" spans="1:14" s="11" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="39"/>
+      <c r="B10" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="30">
         <v>7.1819852465641034</v>
       </c>
-      <c r="E10" s="5">
-        <v>0</v>
+      <c r="D10" s="4">
+        <v>0</v>
+      </c>
+      <c r="E10" s="16">
+        <v>0.4177118021002918</v>
       </c>
       <c r="F10" s="6">
-        <v>0.4177118021002918</v>
-      </c>
-      <c r="G10" s="7">
-        <v>0</v>
-      </c>
-      <c r="H10" s="6">
-        <v>0</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="J10" s="9">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="7">
+        <v>0</v>
+      </c>
+      <c r="I10" s="67">
         <f>[1]Sheet1!$AH$21</f>
         <v>0.55694906946705569</v>
       </c>
-      <c r="K10" s="14">
+      <c r="J10" s="12">
         <f>[1]Sheet1!$AH$22</f>
         <v>0.6961863368338197</v>
       </c>
-      <c r="L10" s="8">
-        <v>0</v>
-      </c>
-      <c r="M10" s="12"/>
-      <c r="N10" s="12"/>
-      <c r="O10" s="12"/>
+      <c r="K10" s="7">
+        <v>0</v>
+      </c>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
     </row>
-    <row r="11" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B11" s="62"/>
-      <c r="C11" s="56" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="50">
+    <row r="11" spans="1:14" s="11" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="40"/>
+      <c r="B11" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="31">
         <v>0.57107699999999995</v>
       </c>
-      <c r="E11" s="5">
+      <c r="D11" s="4">
+        <v>0</v>
+      </c>
+      <c r="E11" s="16">
         <v>0</v>
       </c>
       <c r="F11" s="6">
         <v>0</v>
       </c>
-      <c r="G11" s="7">
-        <v>0</v>
-      </c>
-      <c r="H11" s="6">
-        <v>0</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="J11" s="15">
-        <v>0</v>
-      </c>
-      <c r="K11" s="16">
-        <v>0</v>
-      </c>
-      <c r="L11" s="17">
-        <v>0</v>
-      </c>
-      <c r="M11" s="12"/>
-      <c r="N11" s="12"/>
-      <c r="O11" s="12"/>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="7">
+        <v>0</v>
+      </c>
+      <c r="I11" s="68">
+        <v>0</v>
+      </c>
+      <c r="J11" s="13">
+        <v>0</v>
+      </c>
+      <c r="K11" s="14">
+        <v>0</v>
+      </c>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
     </row>
-    <row r="12" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B12" s="57" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="55" t="s">
+    <row r="12" spans="1:14" s="11" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="32">
+        <v>1.3649733500000001</v>
+      </c>
+      <c r="D12" s="4">
+        <v>5.128305252260053</v>
+      </c>
+      <c r="E12" s="16">
+        <v>0</v>
+      </c>
+      <c r="F12" s="6">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="7">
+        <v>0</v>
+      </c>
+      <c r="I12" s="66">
+        <v>0</v>
+      </c>
+      <c r="J12" s="8">
+        <v>0</v>
+      </c>
+      <c r="K12" s="9">
+        <v>0</v>
+      </c>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
+    </row>
+    <row r="13" spans="1:14" s="11" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="36"/>
+      <c r="B13" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="33">
+        <v>7.5363555180000006</v>
+      </c>
+      <c r="D13" s="4">
+        <v>0</v>
+      </c>
+      <c r="E13" s="16">
+        <v>0</v>
+      </c>
+      <c r="F13" s="6">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0.39807039262342825</v>
+      </c>
+      <c r="H13" s="7">
+        <v>0</v>
+      </c>
+      <c r="I13" s="67">
+        <v>0</v>
+      </c>
+      <c r="J13" s="12">
+        <v>0</v>
+      </c>
+      <c r="K13" s="7">
+        <v>0</v>
+      </c>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+    </row>
+    <row r="14" spans="1:14" s="11" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="36"/>
+      <c r="B14" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="51">
-        <v>1.3649733500000001</v>
-      </c>
-      <c r="E12" s="5">
-        <v>5.128305252260053</v>
-      </c>
-      <c r="F12" s="6">
-        <v>0</v>
-      </c>
-      <c r="G12" s="7">
-        <v>0</v>
-      </c>
-      <c r="H12" s="6">
-        <v>0</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="J12" s="18">
-        <v>0</v>
-      </c>
-      <c r="K12" s="10">
-        <v>0</v>
-      </c>
-      <c r="L12" s="11">
-        <v>0</v>
-      </c>
-      <c r="M12" s="12"/>
-      <c r="N12" s="12"/>
-      <c r="O12" s="12"/>
+      <c r="C14" s="33">
+        <v>2.1255060000000001</v>
+      </c>
+      <c r="D14" s="4">
+        <v>2.8228572396408196</v>
+      </c>
+      <c r="E14" s="16">
+        <v>1.4114286198204098</v>
+      </c>
+      <c r="F14" s="6">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5">
+        <v>1.4114286198204098</v>
+      </c>
+      <c r="H14" s="7">
+        <v>0</v>
+      </c>
+      <c r="I14" s="67">
+        <v>0</v>
+      </c>
+      <c r="J14" s="12">
+        <v>0</v>
+      </c>
+      <c r="K14" s="7">
+        <v>0</v>
+      </c>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
     </row>
-    <row r="13" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B13" s="58"/>
-      <c r="C13" s="19" t="s">
+    <row r="15" spans="1:14" s="11" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="36"/>
+      <c r="B15" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="52">
-        <v>7.5363555180000006</v>
-      </c>
-      <c r="E13" s="5">
-        <v>0</v>
-      </c>
-      <c r="F13" s="6">
-        <v>0</v>
-      </c>
-      <c r="G13" s="7">
-        <v>0</v>
-      </c>
-      <c r="H13" s="6">
-        <v>0.39807039262342825</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="J13" s="9">
-        <v>0</v>
-      </c>
-      <c r="K13" s="14">
-        <v>0</v>
-      </c>
-      <c r="L13" s="8">
-        <v>0</v>
-      </c>
-      <c r="M13" s="12"/>
-      <c r="N13" s="12"/>
-      <c r="O13" s="12"/>
+      <c r="C15" s="33">
+        <v>1.4569589599999999</v>
+      </c>
+      <c r="D15" s="4">
+        <v>4.8045279188921013</v>
+      </c>
+      <c r="E15" s="16">
+        <v>0</v>
+      </c>
+      <c r="F15" s="6">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="7">
+        <v>0</v>
+      </c>
+      <c r="I15" s="67">
+        <v>0</v>
+      </c>
+      <c r="J15" s="12">
+        <v>0</v>
+      </c>
+      <c r="K15" s="7">
+        <v>0</v>
+      </c>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
     </row>
-    <row r="14" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B14" s="58"/>
-      <c r="C14" s="19" t="s">
+    <row r="16" spans="1:14" s="11" customFormat="1" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="37"/>
+      <c r="B16" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="52">
-        <v>2.1255060000000001</v>
-      </c>
-      <c r="E14" s="5">
-        <v>2.8228572396408196</v>
-      </c>
-      <c r="F14" s="6">
-        <v>1.4114286198204098</v>
-      </c>
-      <c r="G14" s="7">
-        <v>0</v>
-      </c>
-      <c r="H14" s="6">
-        <v>1.4114286198204098</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="J14" s="9">
-        <v>0</v>
-      </c>
-      <c r="K14" s="14">
-        <v>0</v>
-      </c>
-      <c r="L14" s="8">
-        <v>0</v>
-      </c>
-      <c r="M14" s="12"/>
-      <c r="N14" s="12"/>
-      <c r="O14" s="12"/>
-    </row>
-    <row r="15" spans="2:15" s="13" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B15" s="58"/>
-      <c r="C15" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" s="52">
-        <v>1.4569589599999999</v>
-      </c>
-      <c r="E15" s="5">
-        <v>4.8045279188921013</v>
-      </c>
-      <c r="F15" s="6">
-        <v>0</v>
-      </c>
-      <c r="G15" s="7">
-        <v>0</v>
-      </c>
-      <c r="H15" s="6">
-        <v>0</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="J15" s="9">
-        <v>0</v>
-      </c>
-      <c r="K15" s="14">
-        <v>0</v>
-      </c>
-      <c r="L15" s="8">
-        <v>0</v>
-      </c>
-      <c r="M15" s="12"/>
-      <c r="N15" s="12"/>
-      <c r="O15" s="12"/>
-    </row>
-    <row r="16" spans="2:15" s="13" customFormat="1" ht="15.45" customHeight="1" thickBot="1">
-      <c r="B16" s="59"/>
-      <c r="C16" s="56" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" s="53">
+      <c r="C16" s="34">
         <v>5.7995670199999996</v>
       </c>
-      <c r="E16" s="20">
-        <v>0</v>
-      </c>
-      <c r="F16" s="21">
-        <v>0</v>
-      </c>
-      <c r="G16" s="22">
+      <c r="D16" s="15">
+        <v>0</v>
+      </c>
+      <c r="E16" s="16">
+        <v>0</v>
+      </c>
+      <c r="F16" s="17">
         <f>[1]Sheet1!$AT$18</f>
         <v>0.17242666505128171</v>
       </c>
-      <c r="H16" s="21">
-        <v>0</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="J16" s="15">
+      <c r="G16" s="16">
+        <v>0</v>
+      </c>
+      <c r="H16" s="14">
+        <v>0</v>
+      </c>
+      <c r="I16" s="68">
         <f>[1]Sheet1!$AT$21</f>
         <v>0.17242666505128171</v>
       </c>
-      <c r="K16" s="16">
-        <v>0</v>
-      </c>
-      <c r="L16" s="17">
-        <v>0</v>
-      </c>
-      <c r="M16" s="12"/>
-      <c r="N16" s="12"/>
-      <c r="O16" s="12"/>
+      <c r="J16" s="13">
+        <v>0</v>
+      </c>
+      <c r="K16" s="14">
+        <v>0</v>
+      </c>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10"/>
     </row>
-    <row r="17" spans="2:29" s="25" customFormat="1">
-      <c r="B17" s="42"/>
-      <c r="C17" s="44" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="54">
+    <row r="17" spans="1:28" s="20" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="51"/>
+      <c r="B17" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="72">
         <v>86.97332109200002</v>
       </c>
-      <c r="E17" s="45">
+      <c r="D17" s="73">
         <v>0.3449333614415635</v>
       </c>
-      <c r="F17" s="45">
+      <c r="E17" s="73">
         <v>0.3449333614415635</v>
       </c>
-      <c r="G17" s="45">
+      <c r="F17" s="73">
         <v>0.3449333614415635</v>
       </c>
-      <c r="H17" s="45">
+      <c r="G17" s="73">
         <v>0.3449333614415635</v>
       </c>
-      <c r="I17" s="46" t="s">
-        <v>4</v>
-      </c>
-      <c r="J17" s="47">
+      <c r="H17" s="74">
+        <v>0</v>
+      </c>
+      <c r="I17" s="75">
         <v>2.8744446786796956E-3</v>
       </c>
-      <c r="K17" s="47">
+      <c r="J17" s="75">
         <v>2.8744446786796956E-3</v>
       </c>
-      <c r="L17" s="47">
+      <c r="K17" s="76">
         <v>2.8744446786796956E-3</v>
       </c>
-      <c r="M17" s="24"/>
-      <c r="N17" s="24"/>
-      <c r="O17" s="24"/>
-      <c r="P17" s="24"/>
-      <c r="Q17" s="24"/>
-      <c r="R17" s="24"/>
-      <c r="S17" s="24"/>
-      <c r="T17" s="24"/>
-      <c r="U17" s="24"/>
-      <c r="V17" s="24"/>
-      <c r="W17" s="24"/>
-      <c r="X17" s="24"/>
-      <c r="Y17" s="24"/>
-      <c r="Z17" s="24"/>
-      <c r="AA17" s="24"/>
-      <c r="AB17" s="24"/>
-      <c r="AC17" s="24"/>
+      <c r="L17" s="19"/>
+      <c r="M17" s="19"/>
+      <c r="N17" s="19"/>
+      <c r="O17" s="19"/>
+      <c r="P17" s="19"/>
+      <c r="Q17" s="19"/>
+      <c r="R17" s="19"/>
+      <c r="S17" s="19"/>
+      <c r="T17" s="19"/>
+      <c r="U17" s="19"/>
+      <c r="V17" s="19"/>
+      <c r="W17" s="19"/>
+      <c r="X17" s="19"/>
+      <c r="Y17" s="19"/>
+      <c r="Z17" s="19"/>
+      <c r="AA17" s="19"/>
+      <c r="AB17" s="19"/>
     </row>
-    <row r="19" spans="2:29" ht="14.55" hidden="1" customHeight="1">
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="28"/>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A18" s="50"/>
     </row>
-    <row r="20" spans="2:29" ht="14.55" hidden="1" customHeight="1">
-      <c r="C20" s="23"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="26"/>
+    <row r="19" spans="1:28" ht="14.55" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="22"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="23"/>
     </row>
-    <row r="21" spans="2:29" ht="14.55" hidden="1" customHeight="1">
-      <c r="C21" s="26"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
+    <row r="20" spans="1:28" ht="14.55" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="21"/>
     </row>
-    <row r="22" spans="2:29" ht="14.55" hidden="1" customHeight="1"/>
-    <row r="23" spans="2:29" ht="14.55" hidden="1" customHeight="1"/>
+    <row r="21" spans="1:28" ht="14.55" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+    </row>
+    <row r="22" spans="1:28" ht="14.55" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="1:28" ht="14.55" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B12:B16"/>
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="C1:L1"/>
-    <mergeCell ref="E2:I2"/>
-    <mergeCell ref="J2:L2"/>
+  <mergeCells count="8">
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A12:A16"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="B1:K1"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="I2:K2"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4:E16">
+  <conditionalFormatting sqref="D4:D16">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$E$17/2"/>
-        <cfvo type="formula" val="$E$17"/>
+        <cfvo type="formula" val="$D$17/2"/>
+        <cfvo type="formula" val="$D$17"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4:F6">
+  <conditionalFormatting sqref="E4:E6">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="#REF!/2"/>
-        <cfvo type="formula" val="#REF!"/>
+        <cfvo type="formula" val="$F$17/2"/>
+        <cfvo type="formula" val="$F$17"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>
@@ -2153,12 +2205,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7:F16">
+  <conditionalFormatting sqref="E4:E16">
     <cfRule type="colorScale" priority="50">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$F$17/2"/>
-        <cfvo type="formula" val="$F$17"/>
+        <cfvo type="formula" val="$E$17/2"/>
+        <cfvo type="formula" val="$E$17"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>
@@ -2195,24 +2247,24 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G16">
+  <conditionalFormatting sqref="F4:F16">
     <cfRule type="colorScale" priority="54">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$G$17/2"/>
-        <cfvo type="formula" val="$G$17"/>
+        <cfvo type="formula" val="$F$17/2"/>
+        <cfvo type="formula" val="$F$17"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H16">
+  <conditionalFormatting sqref="G4:G16">
     <cfRule type="colorScale" priority="55">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$H$17/2"/>
-        <cfvo type="formula" val="$H$17"/>
+        <cfvo type="formula" val="$G$17/2"/>
+        <cfvo type="formula" val="$G$17"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>
@@ -2239,8 +2291,20 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="I4:I16">
+    <cfRule type="colorScale" priority="58">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$I$17/2"/>
+        <cfvo type="formula" val="$I$17"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J4:J16">
-    <cfRule type="colorScale" priority="58">
+    <cfRule type="colorScale" priority="59">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$J$17/2"/>
@@ -2252,7 +2316,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4:K16">
-    <cfRule type="colorScale" priority="59">
+    <cfRule type="colorScale" priority="60">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$K$17/2"/>
@@ -2262,22 +2326,10 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L4:L16">
-    <cfRule type="colorScale" priority="60">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="formula" val="$L$17/2"/>
-        <cfvo type="formula" val="$L$17"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
     <cfRule type="colorScale" priority="61">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="MAX($L$4:$L$16)/2"/>
+        <cfvo type="formula" val="MAX($K$4:$K$16)/2"/>
         <cfvo type="max"/>
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
@@ -2298,7 +2350,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" scale="88" orientation="landscape" r:id="rId1"/>
   <colBreaks count="1" manualBreakCount="1">
-    <brk id="2" max="18" man="1"/>
+    <brk id="1" max="18" man="1"/>
   </colBreaks>
 </worksheet>
 </file>

--- a/data/Heat map 7.xlsx
+++ b/data/Heat map 7.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar-my.sharepoint.com/personal/s_lewis_cgiar_org/Documents/TAAT/R4D/KPIS/Alekeh/for uploads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B2A7F99-962C-44E6-B295-9242338B7068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{BE2A84F2-78F7-4FBF-B462-89D3272FCE9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9AEB69D2-CE8D-4F27-B879-7A064FBA5AAE}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{462AB6D2-C8E4-47A1-AF79-F15809A5475A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{462AB6D2-C8E4-47A1-AF79-F15809A5475A}"/>
   </bookViews>
   <sheets>
     <sheet name="Reputation, Society" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="31">
   <si>
     <t>KPI by $</t>
   </si>
@@ -72,9 +72,6 @@
     <t>Mechanization</t>
   </si>
   <si>
-    <t>per Program Target (target/13)</t>
-  </si>
-  <si>
     <t>Collaboration with Agriculture Research Institutions</t>
   </si>
   <si>
@@ -126,26 +123,30 @@
     <t>Systems Transformation</t>
   </si>
   <si>
-    <t>USD
- (million)</t>
-  </si>
-  <si>
     <t>Biotechnology</t>
   </si>
   <si>
     <t>IITA Program</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>USD (million)</t>
+  </si>
+  <si>
+    <t>per Program Target</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="168" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+  <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="14" x14ac:knownFonts="1">
     <font>
@@ -267,7 +268,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="43">
+  <borders count="44">
     <border>
       <left/>
       <right/>
@@ -369,34 +370,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -451,30 +424,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF00B050"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -492,19 +441,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -548,30 +484,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -634,7 +546,128 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top/>
@@ -645,11 +678,13 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -664,7 +699,7 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -673,48 +708,120 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
+      <right/>
+      <top/>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -723,159 +830,30 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="19" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -886,11 +864,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -899,145 +874,183 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="3" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="40" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="42" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="9" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1063,6 +1076,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Chart1"/>
@@ -1466,663 +1480,660 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" style="28" customWidth="1"/>
-    <col min="2" max="2" width="37.21875" style="10" customWidth="1"/>
-    <col min="3" max="3" width="5.33203125" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.21875" style="24" customWidth="1"/>
-    <col min="5" max="5" width="6.88671875" style="10" customWidth="1"/>
-    <col min="6" max="6" width="6.77734375" style="10" customWidth="1"/>
-    <col min="7" max="7" width="6.21875" style="10" customWidth="1"/>
-    <col min="8" max="8" width="6.77734375" style="10" customWidth="1"/>
-    <col min="9" max="11" width="8.21875" style="10" customWidth="1"/>
-    <col min="12" max="14" width="8.21875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="7.36328125" style="15" customWidth="1"/>
+    <col min="2" max="2" width="37.1796875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="5.36328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.08984375" style="12" customWidth="1"/>
+    <col min="5" max="11" width="7.08984375" style="4" customWidth="1"/>
+    <col min="12" max="14" width="8.1796875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="27" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="26"/>
-      <c r="B1" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="42"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="45"/>
+    <row r="1" spans="1:15" s="14" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="13"/>
+      <c r="B1" s="56" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="57"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="60"/>
     </row>
-    <row r="2" spans="1:14" s="61" customFormat="1" ht="25.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="52"/>
-      <c r="B2" s="54" t="s">
+    <row r="2" spans="1:15" s="16" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="69"/>
+      <c r="B2" s="47" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="64" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="65"/>
+      <c r="K2" s="66"/>
+    </row>
+    <row r="3" spans="1:15" s="3" customFormat="1" ht="117.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="70"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="59" t="s">
-        <v>2</v>
-      </c>
-      <c r="J2" s="59"/>
-      <c r="K2" s="60"/>
-    </row>
-    <row r="3" spans="1:14" s="3" customFormat="1" ht="132" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="53"/>
-      <c r="B3" s="46"/>
-      <c r="C3" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="69" t="s">
+      <c r="D3" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="69" t="s">
+      <c r="F3" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="69" t="s">
+      <c r="G3" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="70" t="s">
+      <c r="H3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="69" t="s">
+      <c r="I3" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="69" t="s">
+      <c r="J3" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="69" t="s">
+      <c r="K3" s="46" t="s">
         <v>16</v>
-      </c>
-      <c r="K3" s="69" t="s">
-        <v>17</v>
       </c>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
     </row>
-    <row r="4" spans="1:14" s="11" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="47" t="s">
+    <row r="4" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="73" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="37">
+        <v>3.4135987800000001</v>
+      </c>
+      <c r="D4" s="21">
+        <v>4.9800814611259021</v>
+      </c>
+      <c r="E4" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="29">
-        <v>3.4135987800000001</v>
-      </c>
-      <c r="D4" s="62">
-        <v>4.9800814611259021</v>
-      </c>
-      <c r="E4" s="63">
-        <v>0</v>
-      </c>
-      <c r="F4" s="64">
+      <c r="F4" s="24">
         <f>[1]Sheet1!$V$18</f>
         <v>0.2929459683015237</v>
       </c>
-      <c r="G4" s="65">
-        <v>0</v>
-      </c>
-      <c r="H4" s="9">
-        <v>0</v>
-      </c>
-      <c r="I4" s="66">
-        <v>0</v>
-      </c>
-      <c r="J4" s="8">
-        <v>0</v>
-      </c>
-      <c r="K4" s="9">
-        <v>0</v>
-      </c>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
+      <c r="G4" s="25">
+        <v>0</v>
+      </c>
+      <c r="H4" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" s="21">
+        <v>0</v>
+      </c>
+      <c r="J4" s="25">
+        <v>0</v>
+      </c>
+      <c r="K4" s="26">
+        <v>0</v>
+      </c>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
     </row>
-    <row r="5" spans="1:14" s="11" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="39"/>
-      <c r="B5" s="48" t="s">
+    <row r="5" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="74"/>
+      <c r="B5" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="38">
         <v>12.720419820000002</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="22">
         <v>1.8081164242580787</v>
       </c>
-      <c r="E5" s="16">
-        <v>0</v>
-      </c>
-      <c r="F5" s="6">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5">
+      <c r="E5" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="28">
+        <v>0</v>
+      </c>
+      <c r="G5" s="29">
         <v>0.23584127272931465</v>
       </c>
-      <c r="H5" s="7">
-        <v>0</v>
-      </c>
-      <c r="I5" s="67">
+      <c r="H5" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" s="22">
         <f>[1]Sheet1!$X$21</f>
         <v>0.15722751515287642</v>
       </c>
-      <c r="J5" s="12">
+      <c r="J5" s="29">
         <f>[1]Sheet1!$X$22</f>
         <v>7.8613757576438209E-2</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5" s="30">
         <f>[1]Sheet1!$X$23</f>
         <v>0.15722751515287642</v>
       </c>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
     </row>
-    <row r="6" spans="1:14" s="11" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="39"/>
-      <c r="B6" s="48" t="s">
+    <row r="6" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="74"/>
+      <c r="B6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="38">
         <v>3.5036499999999999</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="22">
         <v>5.4229161017795731</v>
       </c>
-      <c r="E6" s="16">
-        <v>0</v>
-      </c>
-      <c r="F6" s="6">
-        <v>0</v>
-      </c>
-      <c r="G6" s="5">
+      <c r="E6" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="28">
+        <v>0</v>
+      </c>
+      <c r="G6" s="29">
         <v>0.28541663693576702</v>
       </c>
-      <c r="H6" s="7">
-        <v>0</v>
-      </c>
-      <c r="I6" s="67">
-        <v>0</v>
-      </c>
-      <c r="J6" s="12">
-        <v>0</v>
-      </c>
-      <c r="K6" s="7">
-        <v>0</v>
-      </c>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
+      <c r="H6" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" s="22">
+        <v>0</v>
+      </c>
+      <c r="J6" s="29">
+        <v>0</v>
+      </c>
+      <c r="K6" s="30">
+        <v>0</v>
+      </c>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
     </row>
-    <row r="7" spans="1:14" s="11" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="40"/>
-      <c r="B7" s="49" t="s">
+    <row r="7" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="75"/>
+      <c r="B7" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="39">
         <v>21.304912170000001</v>
       </c>
-      <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="16">
+      <c r="D7" s="23">
+        <v>0</v>
+      </c>
+      <c r="E7" s="27">
         <v>0.65712545014448642</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="32">
         <f>[1]Sheet1!$AB$18</f>
         <v>0.14081259645953281</v>
       </c>
-      <c r="G7" s="5">
-        <v>0</v>
-      </c>
-      <c r="H7" s="7">
-        <v>0</v>
-      </c>
-      <c r="I7" s="68">
+      <c r="G7" s="27">
+        <v>0</v>
+      </c>
+      <c r="H7" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="I7" s="23">
         <f>[1]Sheet1!$AB$21</f>
         <v>0.14081259645953281</v>
       </c>
-      <c r="J7" s="13">
+      <c r="J7" s="27">
         <f>[1]Sheet1!$AB$22</f>
         <v>9.3875064306355213E-2</v>
       </c>
-      <c r="K7" s="14">
+      <c r="K7" s="31">
         <f>[1]Sheet1!$AB$23</f>
         <v>4.6937532153177607E-2</v>
       </c>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
     </row>
-    <row r="8" spans="1:14" s="11" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="38" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="47" t="s">
+    <row r="8" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="73" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="37">
         <v>7.721148311538462</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="21">
         <v>2.3312594543872254</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="25">
         <v>0.12951441413262363</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="24">
         <f>[1]Sheet1!$AD$18</f>
         <v>0.38854324239787086</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="25">
         <v>0.64757207066311817</v>
       </c>
-      <c r="H8" s="7">
-        <v>0</v>
-      </c>
-      <c r="I8" s="66">
+      <c r="H8" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" s="21">
         <f>[1]Sheet1!$AD$21</f>
         <v>0.12951441413262363</v>
       </c>
-      <c r="J8" s="8">
+      <c r="J8" s="25">
         <f>[1]Sheet1!$AD$22</f>
         <v>0.12951441413262363</v>
       </c>
-      <c r="K8" s="9">
-        <v>0</v>
-      </c>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
+      <c r="K8" s="26">
+        <v>0</v>
+      </c>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
     </row>
-    <row r="9" spans="1:14" s="11" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="39"/>
-      <c r="B9" s="48" t="s">
+    <row r="9" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="74"/>
+      <c r="B9" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="38">
         <v>12.273168915897436</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="22">
         <v>3.5035776248709567</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="29">
         <v>1.3851353400652622</v>
       </c>
-      <c r="F9" s="6">
-        <v>0</v>
-      </c>
-      <c r="G9" s="5">
+      <c r="F9" s="28">
+        <v>0</v>
+      </c>
+      <c r="G9" s="29">
         <v>0.24443564824681097</v>
       </c>
-      <c r="H9" s="7">
-        <v>0</v>
-      </c>
-      <c r="I9" s="67">
+      <c r="H9" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="22">
         <f>[1]Sheet1!$AF$21</f>
         <v>0.32591419766241464</v>
       </c>
-      <c r="J9" s="12">
+      <c r="J9" s="29">
         <f>[1]Sheet1!$AF$22</f>
         <v>0.32591419766241464</v>
       </c>
-      <c r="K9" s="7">
+      <c r="K9" s="30">
         <f>[1]Sheet1!$AF$23</f>
         <v>8.147854941560366E-2</v>
       </c>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
     </row>
-    <row r="10" spans="1:14" s="11" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="39"/>
-      <c r="B10" s="48" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="30">
+    <row r="10" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="74"/>
+      <c r="B10" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="38">
         <v>7.1819852465641034</v>
       </c>
-      <c r="D10" s="4">
-        <v>0</v>
-      </c>
-      <c r="E10" s="16">
+      <c r="D10" s="22">
+        <v>0</v>
+      </c>
+      <c r="E10" s="29">
         <v>0.4177118021002918</v>
       </c>
-      <c r="F10" s="6">
-        <v>0</v>
-      </c>
-      <c r="G10" s="5">
-        <v>0</v>
-      </c>
-      <c r="H10" s="7">
-        <v>0</v>
-      </c>
-      <c r="I10" s="67">
+      <c r="F10" s="28">
+        <v>0</v>
+      </c>
+      <c r="G10" s="29">
+        <v>0</v>
+      </c>
+      <c r="H10" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="I10" s="22">
         <f>[1]Sheet1!$AH$21</f>
         <v>0.55694906946705569</v>
       </c>
-      <c r="J10" s="12">
+      <c r="J10" s="29">
         <f>[1]Sheet1!$AH$22</f>
         <v>0.6961863368338197</v>
       </c>
-      <c r="K10" s="7">
-        <v>0</v>
-      </c>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
+      <c r="K10" s="30">
+        <v>0</v>
+      </c>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
     </row>
-    <row r="11" spans="1:14" s="11" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="40"/>
-      <c r="B11" s="49" t="s">
+    <row r="11" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="75"/>
+      <c r="B11" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="39">
         <v>0.57107699999999995</v>
       </c>
-      <c r="D11" s="4">
-        <v>0</v>
-      </c>
-      <c r="E11" s="16">
-        <v>0</v>
-      </c>
-      <c r="F11" s="6">
-        <v>0</v>
-      </c>
-      <c r="G11" s="5">
-        <v>0</v>
-      </c>
-      <c r="H11" s="7">
-        <v>0</v>
-      </c>
-      <c r="I11" s="68">
-        <v>0</v>
-      </c>
-      <c r="J11" s="13">
-        <v>0</v>
-      </c>
-      <c r="K11" s="14">
-        <v>0</v>
-      </c>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
+      <c r="D11" s="23">
+        <v>0</v>
+      </c>
+      <c r="E11" s="27">
+        <v>0</v>
+      </c>
+      <c r="F11" s="32">
+        <v>0</v>
+      </c>
+      <c r="G11" s="27">
+        <v>0</v>
+      </c>
+      <c r="H11" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="I11" s="23">
+        <v>0</v>
+      </c>
+      <c r="J11" s="27">
+        <v>0</v>
+      </c>
+      <c r="K11" s="31">
+        <v>0</v>
+      </c>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
     </row>
-    <row r="12" spans="1:14" s="11" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="47" t="s">
+    <row r="12" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="71" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="49" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="40">
+        <v>1.3649733500000001</v>
+      </c>
+      <c r="D12" s="41">
+        <v>5.128305252260053</v>
+      </c>
+      <c r="E12" s="42">
+        <v>0</v>
+      </c>
+      <c r="F12" s="43">
+        <v>0</v>
+      </c>
+      <c r="G12" s="42">
+        <v>0</v>
+      </c>
+      <c r="H12" s="44" t="s">
+        <v>28</v>
+      </c>
+      <c r="I12" s="41">
+        <v>0</v>
+      </c>
+      <c r="J12" s="42">
+        <v>0</v>
+      </c>
+      <c r="K12" s="44">
+        <v>0</v>
+      </c>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4"/>
+    </row>
+    <row r="13" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="71"/>
+      <c r="B13" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="32">
-        <v>1.3649733500000001</v>
-      </c>
-      <c r="D12" s="4">
-        <v>5.128305252260053</v>
-      </c>
-      <c r="E12" s="16">
-        <v>0</v>
-      </c>
-      <c r="F12" s="6">
-        <v>0</v>
-      </c>
-      <c r="G12" s="5">
-        <v>0</v>
-      </c>
-      <c r="H12" s="7">
-        <v>0</v>
-      </c>
-      <c r="I12" s="66">
-        <v>0</v>
-      </c>
-      <c r="J12" s="8">
-        <v>0</v>
-      </c>
-      <c r="K12" s="9">
-        <v>0</v>
-      </c>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10"/>
+      <c r="C13" s="38">
+        <v>7.5363555180000006</v>
+      </c>
+      <c r="D13" s="22">
+        <v>0</v>
+      </c>
+      <c r="E13" s="29">
+        <v>0</v>
+      </c>
+      <c r="F13" s="28">
+        <v>0</v>
+      </c>
+      <c r="G13" s="29">
+        <v>0.39807039262342825</v>
+      </c>
+      <c r="H13" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="I13" s="22">
+        <v>0</v>
+      </c>
+      <c r="J13" s="29">
+        <v>0</v>
+      </c>
+      <c r="K13" s="30">
+        <v>0</v>
+      </c>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
     </row>
-    <row r="13" spans="1:14" s="11" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="36"/>
-      <c r="B13" s="48" t="s">
+    <row r="14" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="71"/>
+      <c r="B14" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="33">
-        <v>7.5363555180000006</v>
-      </c>
-      <c r="D13" s="4">
-        <v>0</v>
-      </c>
-      <c r="E13" s="16">
-        <v>0</v>
-      </c>
-      <c r="F13" s="6">
-        <v>0</v>
-      </c>
-      <c r="G13" s="5">
-        <v>0.39807039262342825</v>
-      </c>
-      <c r="H13" s="7">
-        <v>0</v>
-      </c>
-      <c r="I13" s="67">
-        <v>0</v>
-      </c>
-      <c r="J13" s="12">
-        <v>0</v>
-      </c>
-      <c r="K13" s="7">
-        <v>0</v>
-      </c>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
+      <c r="C14" s="38">
+        <v>2.1255060000000001</v>
+      </c>
+      <c r="D14" s="22">
+        <v>2.8228572396408196</v>
+      </c>
+      <c r="E14" s="29">
+        <v>1.4114286198204098</v>
+      </c>
+      <c r="F14" s="28">
+        <v>0</v>
+      </c>
+      <c r="G14" s="29">
+        <v>1.4114286198204098</v>
+      </c>
+      <c r="H14" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="I14" s="22">
+        <v>0</v>
+      </c>
+      <c r="J14" s="29">
+        <v>0</v>
+      </c>
+      <c r="K14" s="30">
+        <v>0</v>
+      </c>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
     </row>
-    <row r="14" spans="1:14" s="11" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="36"/>
-      <c r="B14" s="48" t="s">
+    <row r="15" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="71"/>
+      <c r="B15" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="33">
-        <v>2.1255060000000001</v>
-      </c>
-      <c r="D14" s="4">
-        <v>2.8228572396408196</v>
-      </c>
-      <c r="E14" s="16">
-        <v>1.4114286198204098</v>
-      </c>
-      <c r="F14" s="6">
-        <v>0</v>
-      </c>
-      <c r="G14" s="5">
-        <v>1.4114286198204098</v>
-      </c>
-      <c r="H14" s="7">
-        <v>0</v>
-      </c>
-      <c r="I14" s="67">
-        <v>0</v>
-      </c>
-      <c r="J14" s="12">
-        <v>0</v>
-      </c>
-      <c r="K14" s="7">
-        <v>0</v>
-      </c>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10"/>
+      <c r="C15" s="38">
+        <v>1.4569589599999999</v>
+      </c>
+      <c r="D15" s="22">
+        <v>4.8045279188921013</v>
+      </c>
+      <c r="E15" s="29">
+        <v>0</v>
+      </c>
+      <c r="F15" s="28">
+        <v>0</v>
+      </c>
+      <c r="G15" s="29">
+        <v>0</v>
+      </c>
+      <c r="H15" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="I15" s="22">
+        <v>0</v>
+      </c>
+      <c r="J15" s="29">
+        <v>0</v>
+      </c>
+      <c r="K15" s="30">
+        <v>0</v>
+      </c>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="19"/>
     </row>
-    <row r="15" spans="1:14" s="11" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="36"/>
-      <c r="B15" s="48" t="s">
+    <row r="16" spans="1:15" s="5" customFormat="1" ht="15.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="72"/>
+      <c r="B16" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="33">
-        <v>1.4569589599999999</v>
-      </c>
-      <c r="D15" s="4">
-        <v>4.8045279188921013</v>
-      </c>
-      <c r="E15" s="16">
-        <v>0</v>
-      </c>
-      <c r="F15" s="6">
-        <v>0</v>
-      </c>
-      <c r="G15" s="5">
-        <v>0</v>
-      </c>
-      <c r="H15" s="7">
-        <v>0</v>
-      </c>
-      <c r="I15" s="67">
-        <v>0</v>
-      </c>
-      <c r="J15" s="12">
-        <v>0</v>
-      </c>
-      <c r="K15" s="7">
-        <v>0</v>
-      </c>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10"/>
-    </row>
-    <row r="16" spans="1:14" s="11" customFormat="1" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="37"/>
-      <c r="B16" s="49" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="34">
+      <c r="C16" s="39">
         <v>5.7995670199999996</v>
       </c>
-      <c r="D16" s="15">
-        <v>0</v>
-      </c>
-      <c r="E16" s="16">
-        <v>0</v>
-      </c>
-      <c r="F16" s="17">
+      <c r="D16" s="23">
+        <v>0</v>
+      </c>
+      <c r="E16" s="27">
+        <v>0</v>
+      </c>
+      <c r="F16" s="32">
         <f>[1]Sheet1!$AT$18</f>
         <v>0.17242666505128171</v>
       </c>
-      <c r="G16" s="16">
-        <v>0</v>
-      </c>
-      <c r="H16" s="14">
-        <v>0</v>
-      </c>
-      <c r="I16" s="68">
+      <c r="G16" s="27">
+        <v>0</v>
+      </c>
+      <c r="H16" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="I16" s="23">
         <f>[1]Sheet1!$AT$21</f>
         <v>0.17242666505128171</v>
       </c>
-      <c r="J16" s="13">
-        <v>0</v>
-      </c>
-      <c r="K16" s="14">
-        <v>0</v>
-      </c>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="10"/>
+      <c r="J16" s="27">
+        <v>0</v>
+      </c>
+      <c r="K16" s="31">
+        <v>0</v>
+      </c>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
+      <c r="N16" s="4"/>
     </row>
-    <row r="17" spans="1:28" s="20" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="51"/>
-      <c r="B17" s="71" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="72">
+    <row r="17" spans="1:28" s="8" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="67"/>
+      <c r="B17" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="18">
         <v>86.97332109200002</v>
       </c>
-      <c r="D17" s="73">
+      <c r="D17" s="33">
         <v>0.3449333614415635</v>
       </c>
-      <c r="E17" s="73">
+      <c r="E17" s="33">
         <v>0.3449333614415635</v>
       </c>
-      <c r="F17" s="73">
+      <c r="F17" s="33">
         <v>0.3449333614415635</v>
       </c>
-      <c r="G17" s="73">
+      <c r="G17" s="33">
         <v>0.3449333614415635</v>
       </c>
-      <c r="H17" s="74">
-        <v>0</v>
-      </c>
-      <c r="I17" s="75">
+      <c r="H17" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="I17" s="35">
         <v>2.8744446786796956E-3</v>
       </c>
-      <c r="J17" s="75">
+      <c r="J17" s="35">
         <v>2.8744446786796956E-3</v>
       </c>
-      <c r="K17" s="76">
+      <c r="K17" s="36">
         <v>2.8744446786796956E-3</v>
       </c>
-      <c r="L17" s="19"/>
-      <c r="M17" s="19"/>
-      <c r="N17" s="19"/>
-      <c r="O17" s="19"/>
-      <c r="P17" s="19"/>
-      <c r="Q17" s="19"/>
-      <c r="R17" s="19"/>
-      <c r="S17" s="19"/>
-      <c r="T17" s="19"/>
-      <c r="U17" s="19"/>
-      <c r="V17" s="19"/>
-      <c r="W17" s="19"/>
-      <c r="X17" s="19"/>
-      <c r="Y17" s="19"/>
-      <c r="Z17" s="19"/>
-      <c r="AA17" s="19"/>
-      <c r="AB17" s="19"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="7"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7"/>
+      <c r="U17" s="7"/>
+      <c r="V17" s="7"/>
+      <c r="W17" s="7"/>
+      <c r="X17" s="7"/>
+      <c r="Y17" s="7"/>
+      <c r="Z17" s="7"/>
+      <c r="AA17" s="7"/>
+      <c r="AB17" s="7"/>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A18" s="50"/>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A18" s="68"/>
     </row>
-    <row r="19" spans="1:28" ht="14.55" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="22"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="23"/>
+    <row r="19" spans="1:28" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="11"/>
     </row>
-    <row r="20" spans="1:28" ht="14.55" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="21"/>
+    <row r="20" spans="1:28" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="9"/>
     </row>
-    <row r="21" spans="1:28" ht="14.55" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
+    <row r="21" spans="1:28" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
     </row>
-    <row r="22" spans="1:28" ht="14.55" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="23" spans="1:28" ht="14.55" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="1:28" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="23" spans="1:28" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="B1:K1"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="I2:K2"/>
     <mergeCell ref="A17:A18"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A12:A16"/>
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="A8:A11"/>
-    <mergeCell ref="B1:K1"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="I2:K2"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:D16">
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$D$17/2"/>
@@ -2134,7 +2145,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6">
-    <cfRule type="colorScale" priority="7">
+    <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$F$17/2"/>
@@ -2144,7 +2155,7 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="8">
+    <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="MAX(#REF!)/2"/>
@@ -2154,7 +2165,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="9">
+    <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2164,7 +2175,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="10">
+    <cfRule type="colorScale" priority="21">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percent" val="50"/>
@@ -2174,7 +2185,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="11">
+    <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2184,7 +2195,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="12">
+    <cfRule type="colorScale" priority="23">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2194,7 +2205,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="13">
+    <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -2206,7 +2217,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E16">
-    <cfRule type="colorScale" priority="50">
+    <cfRule type="colorScale" priority="61">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$E$17/2"/>
@@ -2216,7 +2227,7 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="51">
+    <cfRule type="colorScale" priority="62">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2226,7 +2237,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="52">
+    <cfRule type="colorScale" priority="63">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percent" val="50"/>
@@ -2236,7 +2247,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="53">
+    <cfRule type="colorScale" priority="64">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2248,7 +2259,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F16">
-    <cfRule type="colorScale" priority="54">
+    <cfRule type="colorScale" priority="65">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$F$17/2"/>
@@ -2260,7 +2271,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G16">
-    <cfRule type="colorScale" priority="55">
+    <cfRule type="colorScale" priority="66">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$G$17/2"/>
@@ -2270,7 +2281,7 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="56">
+    <cfRule type="colorScale" priority="67">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2280,7 +2291,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="57">
+    <cfRule type="colorScale" priority="68">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2291,8 +2302,120 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="H4:H16">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$F$17/2"/>
+        <cfvo type="formula" val="$F$17"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="MAX(#REF!)/2"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percent" val="50"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$E$17/2"/>
+        <cfvo type="formula" val="$E$17"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percent" val="50"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="I4:I16">
-    <cfRule type="colorScale" priority="58">
+    <cfRule type="colorScale" priority="69">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$I$17/2"/>
@@ -2304,7 +2427,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4:J16">
-    <cfRule type="colorScale" priority="59">
+    <cfRule type="colorScale" priority="70">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$J$17/2"/>
@@ -2316,7 +2439,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4:K16">
-    <cfRule type="colorScale" priority="60">
+    <cfRule type="colorScale" priority="71">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$K$17/2"/>
@@ -2326,7 +2449,7 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="61">
+    <cfRule type="colorScale" priority="72">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="MAX($K$4:$K$16)/2"/>
@@ -2336,7 +2459,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="62">
+    <cfRule type="colorScale" priority="73">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/data/Heat map 7.xlsx
+++ b/data/Heat map 7.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar-my.sharepoint.com/personal/s_lewis_cgiar_org/Documents/TAAT/R4D/KPIS/Alekeh/for uploads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{BE2A84F2-78F7-4FBF-B462-89D3272FCE9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9AEB69D2-CE8D-4F27-B879-7A064FBA5AAE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5F7C1BB-5005-4792-B5C0-7E13DAC7000A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{462AB6D2-C8E4-47A1-AF79-F15809A5475A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{462AB6D2-C8E4-47A1-AF79-F15809A5475A}"/>
   </bookViews>
   <sheets>
     <sheet name="Reputation, Society" sheetId="1" r:id="rId1"/>
@@ -142,10 +142,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="14" x14ac:knownFonts="1">
@@ -840,20 +839,20 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -864,7 +863,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -923,17 +922,11 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="3" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -991,6 +984,33 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="3" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1076,7 +1096,6 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Chart1"/>
@@ -1102,54 +1121,6 @@
           </cell>
           <cell r="AT18">
             <v>0.17242666505128171</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="X21">
-            <v>0.15722751515287642</v>
-          </cell>
-          <cell r="AB21">
-            <v>0.14081259645953281</v>
-          </cell>
-          <cell r="AD21">
-            <v>0.12951441413262363</v>
-          </cell>
-          <cell r="AF21">
-            <v>0.32591419766241464</v>
-          </cell>
-          <cell r="AH21">
-            <v>0.55694906946705569</v>
-          </cell>
-          <cell r="AT21">
-            <v>0.17242666505128171</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="X22">
-            <v>7.8613757576438209E-2</v>
-          </cell>
-          <cell r="AB22">
-            <v>9.3875064306355213E-2</v>
-          </cell>
-          <cell r="AD22">
-            <v>0.12951441413262363</v>
-          </cell>
-          <cell r="AF22">
-            <v>0.32591419766241464</v>
-          </cell>
-          <cell r="AH22">
-            <v>0.6961863368338197</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="X23">
-            <v>0.15722751515287642</v>
-          </cell>
-          <cell r="AB23">
-            <v>4.6937532153177607E-2</v>
-          </cell>
-          <cell r="AF23">
-            <v>8.147854941560366E-2</v>
           </cell>
         </row>
       </sheetData>
@@ -1480,92 +1451,92 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB23"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.36328125" style="15" customWidth="1"/>
-    <col min="2" max="2" width="37.1796875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="5.36328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.08984375" style="12" customWidth="1"/>
-    <col min="5" max="11" width="7.08984375" style="4" customWidth="1"/>
-    <col min="12" max="14" width="8.1796875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" style="15" customWidth="1"/>
+    <col min="2" max="2" width="37.21875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="4.77734375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="7.109375" style="12" customWidth="1"/>
+    <col min="5" max="11" width="7.109375" style="4" customWidth="1"/>
+    <col min="12" max="14" width="8.21875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="14" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:15" s="14" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="13"/>
-      <c r="B1" s="56" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="57"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
-      <c r="K1" s="60"/>
+      <c r="B1" s="63" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="64"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="67"/>
     </row>
-    <row r="2" spans="1:15" s="16" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="69"/>
-      <c r="B2" s="47" t="s">
+    <row r="2" spans="1:15" s="16" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="76"/>
+      <c r="B2" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="61" t="s">
+      <c r="C2" s="52"/>
+      <c r="D2" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="63"/>
-      <c r="I2" s="64" t="s">
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="65"/>
-      <c r="K2" s="66"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="73"/>
     </row>
-    <row r="3" spans="1:15" s="3" customFormat="1" ht="117.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="70"/>
-      <c r="B3" s="48"/>
+    <row r="3" spans="1:15" s="3" customFormat="1" ht="117.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="77"/>
+      <c r="B3" s="46"/>
       <c r="C3" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="55" t="s">
+      <c r="D3" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="45" t="s">
+      <c r="E3" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="45" t="s">
+      <c r="F3" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="45" t="s">
+      <c r="G3" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="46" t="s">
+      <c r="H3" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="55" t="s">
+      <c r="I3" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="45" t="s">
+      <c r="J3" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="K3" s="46" t="s">
+      <c r="K3" s="44" t="s">
         <v>16</v>
       </c>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
     </row>
-    <row r="4" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="73" t="s">
+    <row r="4" spans="1:15" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="52" t="s">
+      <c r="B4" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="37">
+      <c r="C4" s="35">
         <v>3.4135987800000001</v>
       </c>
       <c r="D4" s="21">
@@ -1597,12 +1568,12 @@
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
     </row>
-    <row r="5" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="74"/>
-      <c r="B5" s="50" t="s">
+    <row r="5" spans="1:15" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="81"/>
+      <c r="B5" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="38">
+      <c r="C5" s="36">
         <v>12.720419820000002</v>
       </c>
       <c r="D5" s="22">
@@ -1620,28 +1591,25 @@
       <c r="H5" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="I5" s="22">
-        <f>[1]Sheet1!$X$21</f>
-        <v>0.15722751515287642</v>
-      </c>
-      <c r="J5" s="29">
-        <f>[1]Sheet1!$X$22</f>
-        <v>7.8613757576438209E-2</v>
-      </c>
-      <c r="K5" s="30">
-        <f>[1]Sheet1!$X$23</f>
-        <v>0.15722751515287642</v>
+      <c r="I5" s="59">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="J5" s="60">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="K5" s="61">
+        <v>0.28999999999999998</v>
       </c>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
     </row>
-    <row r="6" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="74"/>
-      <c r="B6" s="50" t="s">
+    <row r="6" spans="1:15" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="81"/>
+      <c r="B6" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="38">
+      <c r="C6" s="36">
         <v>3.5036499999999999</v>
       </c>
       <c r="D6" s="22">
@@ -1672,12 +1640,12 @@
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
     </row>
-    <row r="7" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="75"/>
-      <c r="B7" s="51" t="s">
+    <row r="7" spans="1:15" s="5" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="82"/>
+      <c r="B7" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="39">
+      <c r="C7" s="37">
         <v>21.304912170000001</v>
       </c>
       <c r="D7" s="23">
@@ -1696,30 +1664,27 @@
       <c r="H7" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="23">
-        <f>[1]Sheet1!$AB$21</f>
-        <v>0.14081259645953281</v>
-      </c>
-      <c r="J7" s="27">
-        <f>[1]Sheet1!$AB$22</f>
-        <v>9.3875064306355213E-2</v>
-      </c>
-      <c r="K7" s="31">
-        <f>[1]Sheet1!$AB$23</f>
-        <v>4.6937532153177607E-2</v>
+      <c r="I7" s="55">
+        <v>0.43</v>
+      </c>
+      <c r="J7" s="56">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="K7" s="62">
+        <v>0.14000000000000001</v>
       </c>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>
     </row>
-    <row r="8" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="73" t="s">
+    <row r="8" spans="1:15" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="80" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="52" t="s">
+      <c r="B8" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="37">
+      <c r="C8" s="35">
         <v>7.721148311538462</v>
       </c>
       <c r="D8" s="21">
@@ -1738,13 +1703,11 @@
       <c r="H8" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="I8" s="21">
-        <f>[1]Sheet1!$AD$21</f>
-        <v>0.12951441413262363</v>
-      </c>
-      <c r="J8" s="25">
-        <f>[1]Sheet1!$AD$22</f>
-        <v>0.12951441413262363</v>
+      <c r="I8" s="57">
+        <v>0.33</v>
+      </c>
+      <c r="J8" s="58">
+        <v>0.33</v>
       </c>
       <c r="K8" s="26">
         <v>0</v>
@@ -1753,12 +1716,12 @@
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
     </row>
-    <row r="9" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="74"/>
-      <c r="B9" s="50" t="s">
+    <row r="9" spans="1:15" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="81"/>
+      <c r="B9" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="38">
+      <c r="C9" s="36">
         <v>12.273168915897436</v>
       </c>
       <c r="D9" s="22">
@@ -1776,28 +1739,25 @@
       <c r="H9" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="I9" s="22">
-        <f>[1]Sheet1!$AF$21</f>
-        <v>0.32591419766241464</v>
-      </c>
-      <c r="J9" s="29">
-        <f>[1]Sheet1!$AF$22</f>
-        <v>0.32591419766241464</v>
-      </c>
-      <c r="K9" s="30">
-        <f>[1]Sheet1!$AF$23</f>
-        <v>8.147854941560366E-2</v>
+      <c r="I9" s="59">
+        <v>0.44</v>
+      </c>
+      <c r="J9" s="60">
+        <v>0.44</v>
+      </c>
+      <c r="K9" s="61">
+        <v>0.11</v>
       </c>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>
     </row>
-    <row r="10" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="74"/>
-      <c r="B10" s="50" t="s">
+    <row r="10" spans="1:15" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="81"/>
+      <c r="B10" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="38">
+      <c r="C10" s="36">
         <v>7.1819852465641034</v>
       </c>
       <c r="D10" s="22">
@@ -1815,13 +1775,11 @@
       <c r="H10" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="I10" s="22">
-        <f>[1]Sheet1!$AH$21</f>
-        <v>0.55694906946705569</v>
-      </c>
-      <c r="J10" s="29">
-        <f>[1]Sheet1!$AH$22</f>
-        <v>0.6961863368338197</v>
+      <c r="I10" s="59">
+        <v>0.71</v>
+      </c>
+      <c r="J10" s="60">
+        <v>0.71</v>
       </c>
       <c r="K10" s="30">
         <v>0</v>
@@ -1830,12 +1788,12 @@
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
     </row>
-    <row r="11" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="75"/>
-      <c r="B11" s="51" t="s">
+    <row r="11" spans="1:15" s="5" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="82"/>
+      <c r="B11" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="39">
+      <c r="C11" s="37">
         <v>0.57107699999999995</v>
       </c>
       <c r="D11" s="23">
@@ -1866,50 +1824,50 @@
       <c r="M11" s="4"/>
       <c r="N11" s="4"/>
     </row>
-    <row r="12" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="71" t="s">
+    <row r="12" spans="1:15" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="49" t="s">
+      <c r="B12" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="40">
+      <c r="C12" s="38">
         <v>1.3649733500000001</v>
       </c>
-      <c r="D12" s="41">
+      <c r="D12" s="39">
         <v>5.128305252260053</v>
       </c>
-      <c r="E12" s="42">
-        <v>0</v>
-      </c>
-      <c r="F12" s="43">
-        <v>0</v>
-      </c>
-      <c r="G12" s="42">
-        <v>0</v>
-      </c>
-      <c r="H12" s="44" t="s">
+      <c r="E12" s="40">
+        <v>0</v>
+      </c>
+      <c r="F12" s="41">
+        <v>0</v>
+      </c>
+      <c r="G12" s="40">
+        <v>0</v>
+      </c>
+      <c r="H12" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="I12" s="41">
-        <v>0</v>
-      </c>
-      <c r="J12" s="42">
-        <v>0</v>
-      </c>
-      <c r="K12" s="44">
+      <c r="I12" s="39">
+        <v>0</v>
+      </c>
+      <c r="J12" s="40">
+        <v>0</v>
+      </c>
+      <c r="K12" s="42">
         <v>0</v>
       </c>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
       <c r="N12" s="4"/>
     </row>
-    <row r="13" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="71"/>
-      <c r="B13" s="50" t="s">
+    <row r="13" spans="1:15" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="78"/>
+      <c r="B13" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="38">
+      <c r="C13" s="36">
         <v>7.5363555180000006</v>
       </c>
       <c r="D13" s="22">
@@ -1940,12 +1898,12 @@
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
     </row>
-    <row r="14" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="71"/>
-      <c r="B14" s="50" t="s">
+    <row r="14" spans="1:15" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="78"/>
+      <c r="B14" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="38">
+      <c r="C14" s="36">
         <v>2.1255060000000001</v>
       </c>
       <c r="D14" s="22">
@@ -1976,12 +1934,12 @@
       <c r="M14" s="4"/>
       <c r="N14" s="4"/>
     </row>
-    <row r="15" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="71"/>
-      <c r="B15" s="50" t="s">
+    <row r="15" spans="1:15" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="78"/>
+      <c r="B15" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="38">
+      <c r="C15" s="36">
         <v>1.4569589599999999</v>
       </c>
       <c r="D15" s="22">
@@ -2013,12 +1971,12 @@
       <c r="N15" s="4"/>
       <c r="O15" s="19"/>
     </row>
-    <row r="16" spans="1:15" s="5" customFormat="1" ht="15.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="72"/>
-      <c r="B16" s="53" t="s">
+    <row r="16" spans="1:15" s="5" customFormat="1" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="79"/>
+      <c r="B16" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="39">
+      <c r="C16" s="37">
         <v>5.7995670199999996</v>
       </c>
       <c r="D16" s="23">
@@ -2037,9 +1995,8 @@
       <c r="H16" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="I16" s="23">
-        <f>[1]Sheet1!$AT$21</f>
-        <v>0.17242666505128171</v>
+      <c r="I16" s="55">
+        <v>1</v>
       </c>
       <c r="J16" s="27">
         <v>0</v>
@@ -2051,8 +2008,8 @@
       <c r="M16" s="4"/>
       <c r="N16" s="4"/>
     </row>
-    <row r="17" spans="1:28" s="8" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="67"/>
+    <row r="17" spans="1:28" s="8" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="74"/>
       <c r="B17" s="17" t="s">
         <v>30</v>
       </c>
@@ -2074,14 +2031,14 @@
       <c r="H17" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="I17" s="35">
-        <v>2.8744446786796956E-3</v>
-      </c>
-      <c r="J17" s="35">
-        <v>2.8744446786796956E-3</v>
-      </c>
-      <c r="K17" s="36">
-        <v>2.8744446786796956E-3</v>
+      <c r="I17" s="54">
+        <v>0.25</v>
+      </c>
+      <c r="J17" s="54">
+        <v>0.25</v>
+      </c>
+      <c r="K17" s="54">
+        <v>0.25</v>
       </c>
       <c r="L17" s="7"/>
       <c r="M17" s="7"/>
@@ -2101,26 +2058,26 @@
       <c r="AA17" s="7"/>
       <c r="AB17" s="7"/>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A18" s="68"/>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A18" s="75"/>
     </row>
-    <row r="19" spans="1:28" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:28" ht="14.55" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
       <c r="D19" s="11"/>
     </row>
-    <row r="20" spans="1:28" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:28" ht="14.55" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
       <c r="D20" s="9"/>
     </row>
-    <row r="21" spans="1:28" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:28" ht="14.55" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
     </row>
-    <row r="22" spans="1:28" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="23" spans="1:28" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="22" spans="1:28" ht="14.55" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="1:28" ht="14.55" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="B1:K1"/>

--- a/data/Heat map 7.xlsx
+++ b/data/Heat map 7.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar-my.sharepoint.com/personal/s_lewis_cgiar_org/Documents/TAAT/R4D/KPIS/Alekeh/for uploads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5F7C1BB-5005-4792-B5C0-7E13DAC7000A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="123" documentId="8_{BE2A84F2-78F7-4FBF-B462-89D3272FCE9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1AF9186-E89C-4BD2-A862-A64C7774CBCF}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{462AB6D2-C8E4-47A1-AF79-F15809A5475A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{462AB6D2-C8E4-47A1-AF79-F15809A5475A}"/>
   </bookViews>
   <sheets>
     <sheet name="Reputation, Society" sheetId="1" r:id="rId1"/>
@@ -143,9 +143,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="14" x14ac:knownFonts="1">
     <font>
@@ -839,20 +839,20 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -863,7 +863,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -879,75 +879,36 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="40" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1010,6 +971,57 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="39" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="40" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="41" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="40" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1096,19 +1108,14 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Chart1"/>
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
-        <row r="12">
-          <cell r="I12">
-            <v>1.4999999999999999E-2</v>
-          </cell>
-        </row>
         <row r="18">
           <cell r="V18">
             <v>0.2929459683015237</v>
@@ -1451,519 +1458,519 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" style="15" customWidth="1"/>
-    <col min="2" max="2" width="37.21875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="4.77734375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="7.109375" style="12" customWidth="1"/>
-    <col min="5" max="11" width="7.109375" style="4" customWidth="1"/>
-    <col min="12" max="14" width="8.21875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="7.36328125" style="15" customWidth="1"/>
+    <col min="2" max="2" width="37.1796875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="5.08984375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="7.08984375" style="12" customWidth="1"/>
+    <col min="5" max="11" width="7.08984375" style="4" customWidth="1"/>
+    <col min="12" max="14" width="8.1796875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="14" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" s="14" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="13"/>
-      <c r="B1" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="64"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="66"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="67"/>
+      <c r="B1" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="68"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="71"/>
     </row>
-    <row r="2" spans="1:15" s="16" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="76"/>
-      <c r="B2" s="45" t="s">
+    <row r="2" spans="1:15" s="16" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="80"/>
+      <c r="B2" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="68" t="s">
+      <c r="C2" s="39"/>
+      <c r="D2" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="71" t="s">
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="74"/>
+      <c r="I2" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="72"/>
-      <c r="K2" s="73"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="77"/>
     </row>
-    <row r="3" spans="1:15" s="3" customFormat="1" ht="117.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="77"/>
-      <c r="B3" s="46"/>
+    <row r="3" spans="1:15" s="3" customFormat="1" ht="117.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="81"/>
+      <c r="B3" s="33"/>
       <c r="C3" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="53" t="s">
+      <c r="D3" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="43" t="s">
+      <c r="E3" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="43" t="s">
+      <c r="F3" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="43" t="s">
+      <c r="G3" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="44" t="s">
+      <c r="H3" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="53" t="s">
+      <c r="I3" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="43" t="s">
+      <c r="J3" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="K3" s="44" t="s">
+      <c r="K3" s="31" t="s">
         <v>16</v>
       </c>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
     </row>
-    <row r="4" spans="1:15" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="80" t="s">
+    <row r="4" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="50" t="s">
+      <c r="B4" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="35">
+      <c r="C4" s="25">
         <v>3.4135987800000001</v>
       </c>
-      <c r="D4" s="21">
+      <c r="D4" s="56">
         <v>4.9800814611259021</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="24">
+      <c r="F4" s="58">
         <f>[1]Sheet1!$V$18</f>
         <v>0.2929459683015237</v>
       </c>
-      <c r="G4" s="25">
-        <v>0</v>
-      </c>
-      <c r="H4" s="26" t="s">
+      <c r="G4" s="57">
+        <v>0</v>
+      </c>
+      <c r="H4" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="I4" s="21">
-        <v>0</v>
-      </c>
-      <c r="J4" s="25">
-        <v>0</v>
-      </c>
-      <c r="K4" s="26">
+      <c r="I4" s="44">
+        <v>0</v>
+      </c>
+      <c r="J4" s="45">
+        <v>0</v>
+      </c>
+      <c r="K4" s="50">
         <v>0</v>
       </c>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
     </row>
-    <row r="5" spans="1:15" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="81"/>
-      <c r="B5" s="48" t="s">
+    <row r="5" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="85"/>
+      <c r="B5" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="36">
+      <c r="C5" s="26">
         <v>12.720419820000002</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="59">
         <v>1.8081164242580787</v>
       </c>
-      <c r="E5" s="29" t="s">
+      <c r="E5" s="60" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="28">
-        <v>0</v>
-      </c>
-      <c r="G5" s="29">
+      <c r="F5" s="61">
+        <v>0</v>
+      </c>
+      <c r="G5" s="60">
         <v>0.23584127272931465</v>
       </c>
-      <c r="H5" s="30" t="s">
+      <c r="H5" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="I5" s="59">
+      <c r="I5" s="46">
         <v>0.28999999999999998</v>
       </c>
-      <c r="J5" s="60">
+      <c r="J5" s="47">
         <v>0.14000000000000001</v>
       </c>
-      <c r="K5" s="61">
+      <c r="K5" s="48">
         <v>0.28999999999999998</v>
       </c>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
     </row>
-    <row r="6" spans="1:15" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="81"/>
-      <c r="B6" s="48" t="s">
+    <row r="6" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="85"/>
+      <c r="B6" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="36">
+      <c r="C6" s="26">
         <v>3.5036499999999999</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="59">
         <v>5.4229161017795731</v>
       </c>
-      <c r="E6" s="29" t="s">
+      <c r="E6" s="60" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="28">
-        <v>0</v>
-      </c>
-      <c r="G6" s="29">
+      <c r="F6" s="61">
+        <v>0</v>
+      </c>
+      <c r="G6" s="60">
         <v>0.28541663693576702</v>
       </c>
-      <c r="H6" s="30" t="s">
+      <c r="H6" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="22">
-        <v>0</v>
-      </c>
-      <c r="J6" s="29">
-        <v>0</v>
-      </c>
-      <c r="K6" s="30">
+      <c r="I6" s="46">
+        <v>0</v>
+      </c>
+      <c r="J6" s="47">
+        <v>0</v>
+      </c>
+      <c r="K6" s="48">
         <v>0</v>
       </c>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
     </row>
-    <row r="7" spans="1:15" s="5" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="82"/>
-      <c r="B7" s="49" t="s">
+    <row r="7" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="86"/>
+      <c r="B7" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="37">
+      <c r="C7" s="27">
         <v>21.304912170000001</v>
       </c>
-      <c r="D7" s="23">
-        <v>0</v>
-      </c>
-      <c r="E7" s="27">
+      <c r="D7" s="55">
+        <v>0</v>
+      </c>
+      <c r="E7" s="62">
         <v>0.65712545014448642</v>
       </c>
-      <c r="F7" s="32">
+      <c r="F7" s="63">
         <f>[1]Sheet1!$AB$18</f>
         <v>0.14081259645953281</v>
       </c>
-      <c r="G7" s="27">
-        <v>0</v>
-      </c>
-      <c r="H7" s="31" t="s">
+      <c r="G7" s="62">
+        <v>0</v>
+      </c>
+      <c r="H7" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="55">
+      <c r="I7" s="42">
         <v>0.43</v>
       </c>
-      <c r="J7" s="56">
+      <c r="J7" s="43">
         <v>0.28999999999999998</v>
       </c>
-      <c r="K7" s="62">
+      <c r="K7" s="49">
         <v>0.14000000000000001</v>
       </c>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>
     </row>
-    <row r="8" spans="1:15" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="80" t="s">
+    <row r="8" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="50" t="s">
+      <c r="B8" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="35">
+      <c r="C8" s="25">
         <v>7.721148311538462</v>
       </c>
-      <c r="D8" s="21">
+      <c r="D8" s="56">
         <v>2.3312594543872254</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="57">
         <v>0.12951441413262363</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="58">
         <f>[1]Sheet1!$AD$18</f>
         <v>0.38854324239787086</v>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="57">
         <v>0.64757207066311817</v>
       </c>
-      <c r="H8" s="26" t="s">
+      <c r="H8" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="I8" s="57">
+      <c r="I8" s="44">
         <v>0.33</v>
       </c>
-      <c r="J8" s="58">
+      <c r="J8" s="45">
         <v>0.33</v>
       </c>
-      <c r="K8" s="26">
+      <c r="K8" s="50">
         <v>0</v>
       </c>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
     </row>
-    <row r="9" spans="1:15" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="81"/>
-      <c r="B9" s="48" t="s">
+    <row r="9" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="85"/>
+      <c r="B9" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="36">
+      <c r="C9" s="26">
         <v>12.273168915897436</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="59">
         <v>3.5035776248709567</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="60">
         <v>1.3851353400652622</v>
       </c>
-      <c r="F9" s="28">
-        <v>0</v>
-      </c>
-      <c r="G9" s="29">
+      <c r="F9" s="61">
+        <v>0</v>
+      </c>
+      <c r="G9" s="60">
         <v>0.24443564824681097</v>
       </c>
-      <c r="H9" s="30" t="s">
+      <c r="H9" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="I9" s="59">
+      <c r="I9" s="46">
         <v>0.44</v>
       </c>
-      <c r="J9" s="60">
+      <c r="J9" s="47">
         <v>0.44</v>
       </c>
-      <c r="K9" s="61">
+      <c r="K9" s="48">
         <v>0.11</v>
       </c>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>
     </row>
-    <row r="10" spans="1:15" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="81"/>
-      <c r="B10" s="48" t="s">
+    <row r="10" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="85"/>
+      <c r="B10" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="36">
+      <c r="C10" s="26">
         <v>7.1819852465641034</v>
       </c>
-      <c r="D10" s="22">
-        <v>0</v>
-      </c>
-      <c r="E10" s="29">
+      <c r="D10" s="59">
+        <v>0</v>
+      </c>
+      <c r="E10" s="60">
         <v>0.4177118021002918</v>
       </c>
-      <c r="F10" s="28">
-        <v>0</v>
-      </c>
-      <c r="G10" s="29">
-        <v>0</v>
-      </c>
-      <c r="H10" s="30" t="s">
+      <c r="F10" s="61">
+        <v>0</v>
+      </c>
+      <c r="G10" s="60">
+        <v>0</v>
+      </c>
+      <c r="H10" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="I10" s="59">
+      <c r="I10" s="46">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="J10" s="47">
         <v>0.71</v>
       </c>
-      <c r="J10" s="60">
-        <v>0.71</v>
-      </c>
-      <c r="K10" s="30">
+      <c r="K10" s="48">
         <v>0</v>
       </c>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
     </row>
-    <row r="11" spans="1:15" s="5" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="82"/>
-      <c r="B11" s="49" t="s">
+    <row r="11" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="86"/>
+      <c r="B11" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="37">
+      <c r="C11" s="27">
         <v>0.57107699999999995</v>
       </c>
-      <c r="D11" s="23">
-        <v>0</v>
-      </c>
-      <c r="E11" s="27">
-        <v>0</v>
-      </c>
-      <c r="F11" s="32">
-        <v>0</v>
-      </c>
-      <c r="G11" s="27">
-        <v>0</v>
-      </c>
-      <c r="H11" s="31" t="s">
+      <c r="D11" s="55">
+        <v>0</v>
+      </c>
+      <c r="E11" s="62">
+        <v>0</v>
+      </c>
+      <c r="F11" s="63">
+        <v>0</v>
+      </c>
+      <c r="G11" s="62">
+        <v>0</v>
+      </c>
+      <c r="H11" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="I11" s="23">
-        <v>0</v>
-      </c>
-      <c r="J11" s="27">
-        <v>0</v>
-      </c>
-      <c r="K11" s="31">
+      <c r="I11" s="42">
+        <v>0</v>
+      </c>
+      <c r="J11" s="43">
+        <v>0</v>
+      </c>
+      <c r="K11" s="49">
         <v>0</v>
       </c>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
       <c r="N11" s="4"/>
     </row>
-    <row r="12" spans="1:15" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="78" t="s">
+    <row r="12" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="47" t="s">
+      <c r="B12" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="38">
+      <c r="C12" s="28">
         <v>1.3649733500000001</v>
       </c>
-      <c r="D12" s="39">
+      <c r="D12" s="64">
         <v>5.128305252260053</v>
       </c>
-      <c r="E12" s="40">
-        <v>0</v>
-      </c>
-      <c r="F12" s="41">
-        <v>0</v>
-      </c>
-      <c r="G12" s="40">
-        <v>0</v>
-      </c>
-      <c r="H12" s="42" t="s">
+      <c r="E12" s="65">
+        <v>0</v>
+      </c>
+      <c r="F12" s="66">
+        <v>0</v>
+      </c>
+      <c r="G12" s="65">
+        <v>0</v>
+      </c>
+      <c r="H12" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="I12" s="39">
-        <v>0</v>
-      </c>
-      <c r="J12" s="40">
-        <v>0</v>
-      </c>
-      <c r="K12" s="42">
+      <c r="I12" s="51">
+        <v>0</v>
+      </c>
+      <c r="J12" s="52">
+        <v>0</v>
+      </c>
+      <c r="K12" s="53">
         <v>0</v>
       </c>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
       <c r="N12" s="4"/>
     </row>
-    <row r="13" spans="1:15" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="78"/>
-      <c r="B13" s="48" t="s">
+    <row r="13" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="82"/>
+      <c r="B13" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="36">
+      <c r="C13" s="26">
         <v>7.5363555180000006</v>
       </c>
-      <c r="D13" s="22">
-        <v>0</v>
-      </c>
-      <c r="E13" s="29">
-        <v>0</v>
-      </c>
-      <c r="F13" s="28">
-        <v>0</v>
-      </c>
-      <c r="G13" s="29">
+      <c r="D13" s="59">
+        <v>0</v>
+      </c>
+      <c r="E13" s="60">
+        <v>0</v>
+      </c>
+      <c r="F13" s="61">
+        <v>0</v>
+      </c>
+      <c r="G13" s="60">
         <v>0.39807039262342825</v>
       </c>
-      <c r="H13" s="30" t="s">
+      <c r="H13" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="I13" s="22">
-        <v>0</v>
-      </c>
-      <c r="J13" s="29">
-        <v>0</v>
-      </c>
-      <c r="K13" s="30">
+      <c r="I13" s="46">
+        <v>0</v>
+      </c>
+      <c r="J13" s="47">
+        <v>0</v>
+      </c>
+      <c r="K13" s="48">
         <v>0</v>
       </c>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
     </row>
-    <row r="14" spans="1:15" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="78"/>
-      <c r="B14" s="48" t="s">
+    <row r="14" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="82"/>
+      <c r="B14" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="36">
+      <c r="C14" s="26">
         <v>2.1255060000000001</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="59">
         <v>2.8228572396408196</v>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="60">
         <v>1.4114286198204098</v>
       </c>
-      <c r="F14" s="28">
-        <v>0</v>
-      </c>
-      <c r="G14" s="29">
+      <c r="F14" s="61">
+        <v>0</v>
+      </c>
+      <c r="G14" s="60">
         <v>1.4114286198204098</v>
       </c>
-      <c r="H14" s="30" t="s">
+      <c r="H14" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="I14" s="22">
-        <v>0</v>
-      </c>
-      <c r="J14" s="29">
-        <v>0</v>
-      </c>
-      <c r="K14" s="30">
+      <c r="I14" s="46">
+        <v>0</v>
+      </c>
+      <c r="J14" s="47">
+        <v>0</v>
+      </c>
+      <c r="K14" s="48">
         <v>0</v>
       </c>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
       <c r="N14" s="4"/>
     </row>
-    <row r="15" spans="1:15" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="78"/>
-      <c r="B15" s="48" t="s">
+    <row r="15" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="82"/>
+      <c r="B15" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="36">
+      <c r="C15" s="26">
         <v>1.4569589599999999</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="59">
         <v>4.8045279188921013</v>
       </c>
-      <c r="E15" s="29">
-        <v>0</v>
-      </c>
-      <c r="F15" s="28">
-        <v>0</v>
-      </c>
-      <c r="G15" s="29">
-        <v>0</v>
-      </c>
-      <c r="H15" s="30" t="s">
+      <c r="E15" s="60">
+        <v>0</v>
+      </c>
+      <c r="F15" s="61">
+        <v>0</v>
+      </c>
+      <c r="G15" s="60">
+        <v>0</v>
+      </c>
+      <c r="H15" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="I15" s="22">
-        <v>0</v>
-      </c>
-      <c r="J15" s="29">
-        <v>0</v>
-      </c>
-      <c r="K15" s="30">
+      <c r="I15" s="46">
+        <v>0</v>
+      </c>
+      <c r="J15" s="47">
+        <v>0</v>
+      </c>
+      <c r="K15" s="48">
         <v>0</v>
       </c>
       <c r="L15" s="4"/>
@@ -1971,73 +1978,73 @@
       <c r="N15" s="4"/>
       <c r="O15" s="19"/>
     </row>
-    <row r="16" spans="1:15" s="5" customFormat="1" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="79"/>
-      <c r="B16" s="51" t="s">
+    <row r="16" spans="1:15" s="5" customFormat="1" ht="15.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="83"/>
+      <c r="B16" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="37">
+      <c r="C16" s="27">
         <v>5.7995670199999996</v>
       </c>
-      <c r="D16" s="23">
-        <v>0</v>
-      </c>
-      <c r="E16" s="27">
-        <v>0</v>
-      </c>
-      <c r="F16" s="32">
+      <c r="D16" s="55">
+        <v>0</v>
+      </c>
+      <c r="E16" s="62">
+        <v>0</v>
+      </c>
+      <c r="F16" s="63">
         <f>[1]Sheet1!$AT$18</f>
         <v>0.17242666505128171</v>
       </c>
-      <c r="G16" s="27">
-        <v>0</v>
-      </c>
-      <c r="H16" s="31" t="s">
+      <c r="G16" s="62">
+        <v>0</v>
+      </c>
+      <c r="H16" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="I16" s="55">
+      <c r="I16" s="42">
         <v>1</v>
       </c>
-      <c r="J16" s="27">
-        <v>0</v>
-      </c>
-      <c r="K16" s="31">
+      <c r="J16" s="43">
+        <v>0</v>
+      </c>
+      <c r="K16" s="49">
         <v>0</v>
       </c>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
       <c r="N16" s="4"/>
     </row>
-    <row r="17" spans="1:28" s="8" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="74"/>
+    <row r="17" spans="1:28" s="8" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="78"/>
       <c r="B17" s="17" t="s">
         <v>30</v>
       </c>
       <c r="C17" s="18">
         <v>86.97332109200002</v>
       </c>
-      <c r="D17" s="33">
+      <c r="D17" s="54">
         <v>0.3449333614415635</v>
       </c>
-      <c r="E17" s="33">
+      <c r="E17" s="54">
         <v>0.3449333614415635</v>
       </c>
-      <c r="F17" s="33">
+      <c r="F17" s="54">
         <v>0.3449333614415635</v>
       </c>
-      <c r="G17" s="33">
+      <c r="G17" s="54">
         <v>0.3449333614415635</v>
       </c>
-      <c r="H17" s="34" t="s">
+      <c r="H17" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="I17" s="54">
+      <c r="I17" s="41">
         <v>0.25</v>
       </c>
-      <c r="J17" s="54">
+      <c r="J17" s="41">
         <v>0.25</v>
       </c>
-      <c r="K17" s="54">
+      <c r="K17" s="41">
         <v>0.25</v>
       </c>
       <c r="L17" s="7"/>
@@ -2058,26 +2065,26 @@
       <c r="AA17" s="7"/>
       <c r="AB17" s="7"/>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A18" s="75"/>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A18" s="79"/>
     </row>
-    <row r="19" spans="1:28" ht="14.55" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:28" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
       <c r="D19" s="11"/>
     </row>
-    <row r="20" spans="1:28" ht="14.55" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:28" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
       <c r="D20" s="9"/>
     </row>
-    <row r="21" spans="1:28" ht="14.55" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:28" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
     </row>
-    <row r="22" spans="1:28" ht="14.55" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="23" spans="1:28" ht="14.55" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="1:28" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="23" spans="1:28" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="B1:K1"/>

--- a/data/Heat map 7.xlsx
+++ b/data/Heat map 7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar-my.sharepoint.com/personal/s_lewis_cgiar_org/Documents/TAAT/R4D/KPIS/Alekeh/for uploads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="123" documentId="8_{BE2A84F2-78F7-4FBF-B462-89D3272FCE9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1AF9186-E89C-4BD2-A862-A64C7774CBCF}"/>
+  <xr:revisionPtr revIDLastSave="124" documentId="8_{BE2A84F2-78F7-4FBF-B462-89D3272FCE9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7587A7E-9465-4859-B38A-88F443B2DF50}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{462AB6D2-C8E4-47A1-AF79-F15809A5475A}"/>
   </bookViews>
@@ -142,10 +142,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="14" x14ac:knownFonts="1">
     <font>
@@ -946,45 +947,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="3" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="39" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="40" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="41" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1083,6 +1045,45 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="19" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="39" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="40" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="41" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1115,7 +1116,13 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
+        <row r="12">
+          <cell r="I12">
+            <v>1.4999999999999999E-2</v>
+          </cell>
+        </row>
         <row r="18">
           <cell r="V18">
             <v>0.2929459683015237</v>
@@ -1470,40 +1477,40 @@
   <sheetData>
     <row r="1" spans="1:15" s="14" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="13"/>
-      <c r="B1" s="67" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="68"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
-      <c r="I1" s="70"/>
-      <c r="J1" s="70"/>
-      <c r="K1" s="71"/>
+      <c r="B1" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="55"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="58"/>
     </row>
     <row r="2" spans="1:15" s="16" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="80"/>
+      <c r="A2" s="67"/>
       <c r="B2" s="32" t="s">
         <v>27</v>
       </c>
       <c r="C2" s="39"/>
-      <c r="D2" s="72" t="s">
+      <c r="D2" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="74"/>
-      <c r="I2" s="75" t="s">
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="76"/>
-      <c r="K2" s="77"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="64"/>
     </row>
     <row r="3" spans="1:15" s="3" customFormat="1" ht="117.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="81"/>
+      <c r="A3" s="68"/>
       <c r="B3" s="33"/>
       <c r="C3" s="20" t="s">
         <v>29</v>
@@ -1537,7 +1544,7 @@
       <c r="N3" s="2"/>
     </row>
     <row r="4" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="84" t="s">
+      <c r="A4" s="71" t="s">
         <v>23</v>
       </c>
       <c r="B4" s="37" t="s">
@@ -1546,29 +1553,29 @@
       <c r="C4" s="25">
         <v>3.4135987800000001</v>
       </c>
-      <c r="D4" s="56">
+      <c r="D4" s="43">
         <v>4.9800814611259021</v>
       </c>
-      <c r="E4" s="57" t="s">
+      <c r="E4" s="44" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="58">
+      <c r="F4" s="45">
         <f>[1]Sheet1!$V$18</f>
         <v>0.2929459683015237</v>
       </c>
-      <c r="G4" s="57">
+      <c r="G4" s="44">
         <v>0</v>
       </c>
       <c r="H4" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="I4" s="44">
-        <v>0</v>
-      </c>
-      <c r="J4" s="45">
-        <v>0</v>
-      </c>
-      <c r="K4" s="50">
+      <c r="I4" s="74">
+        <v>0</v>
+      </c>
+      <c r="J4" s="75">
+        <v>0</v>
+      </c>
+      <c r="K4" s="76">
         <v>0</v>
       </c>
       <c r="L4" s="4"/>
@@ -1576,35 +1583,35 @@
       <c r="N4" s="4"/>
     </row>
     <row r="5" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="85"/>
+      <c r="A5" s="72"/>
       <c r="B5" s="35" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="26">
         <v>12.720419820000002</v>
       </c>
-      <c r="D5" s="59">
+      <c r="D5" s="46">
         <v>1.8081164242580787</v>
       </c>
-      <c r="E5" s="60" t="s">
+      <c r="E5" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="61">
-        <v>0</v>
-      </c>
-      <c r="G5" s="60">
+      <c r="F5" s="48">
+        <v>0</v>
+      </c>
+      <c r="G5" s="47">
         <v>0.23584127272931465</v>
       </c>
       <c r="H5" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="I5" s="46">
+      <c r="I5" s="77">
         <v>0.28999999999999998</v>
       </c>
-      <c r="J5" s="47">
+      <c r="J5" s="78">
         <v>0.14000000000000001</v>
       </c>
-      <c r="K5" s="48">
+      <c r="K5" s="79">
         <v>0.28999999999999998</v>
       </c>
       <c r="L5" s="4"/>
@@ -1612,35 +1619,35 @@
       <c r="N5" s="4"/>
     </row>
     <row r="6" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="85"/>
+      <c r="A6" s="72"/>
       <c r="B6" s="35" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="26">
         <v>3.5036499999999999</v>
       </c>
-      <c r="D6" s="59">
+      <c r="D6" s="46">
         <v>5.4229161017795731</v>
       </c>
-      <c r="E6" s="60" t="s">
+      <c r="E6" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="61">
-        <v>0</v>
-      </c>
-      <c r="G6" s="60">
+      <c r="F6" s="48">
+        <v>0</v>
+      </c>
+      <c r="G6" s="47">
         <v>0.28541663693576702</v>
       </c>
       <c r="H6" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="46">
-        <v>0</v>
-      </c>
-      <c r="J6" s="47">
-        <v>0</v>
-      </c>
-      <c r="K6" s="48">
+      <c r="I6" s="77">
+        <v>0</v>
+      </c>
+      <c r="J6" s="78">
+        <v>0</v>
+      </c>
+      <c r="K6" s="79">
         <v>0</v>
       </c>
       <c r="L6" s="4"/>
@@ -1648,36 +1655,36 @@
       <c r="N6" s="4"/>
     </row>
     <row r="7" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="86"/>
+      <c r="A7" s="73"/>
       <c r="B7" s="36" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="27">
         <v>21.304912170000001</v>
       </c>
-      <c r="D7" s="55">
-        <v>0</v>
-      </c>
-      <c r="E7" s="62">
+      <c r="D7" s="42">
+        <v>0</v>
+      </c>
+      <c r="E7" s="49">
         <v>0.65712545014448642</v>
       </c>
-      <c r="F7" s="63">
+      <c r="F7" s="50">
         <f>[1]Sheet1!$AB$18</f>
         <v>0.14081259645953281</v>
       </c>
-      <c r="G7" s="62">
+      <c r="G7" s="49">
         <v>0</v>
       </c>
       <c r="H7" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="42">
+      <c r="I7" s="80">
         <v>0.43</v>
       </c>
-      <c r="J7" s="43">
+      <c r="J7" s="81">
         <v>0.28999999999999998</v>
       </c>
-      <c r="K7" s="49">
+      <c r="K7" s="82">
         <v>0.14000000000000001</v>
       </c>
       <c r="L7" s="4"/>
@@ -1685,7 +1692,7 @@
       <c r="N7" s="4"/>
     </row>
     <row r="8" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="84" t="s">
+      <c r="A8" s="71" t="s">
         <v>24</v>
       </c>
       <c r="B8" s="37" t="s">
@@ -1694,29 +1701,29 @@
       <c r="C8" s="25">
         <v>7.721148311538462</v>
       </c>
-      <c r="D8" s="56">
+      <c r="D8" s="43">
         <v>2.3312594543872254</v>
       </c>
-      <c r="E8" s="57">
+      <c r="E8" s="44">
         <v>0.12951441413262363</v>
       </c>
-      <c r="F8" s="58">
+      <c r="F8" s="45">
         <f>[1]Sheet1!$AD$18</f>
         <v>0.38854324239787086</v>
       </c>
-      <c r="G8" s="57">
+      <c r="G8" s="44">
         <v>0.64757207066311817</v>
       </c>
       <c r="H8" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="I8" s="44">
+      <c r="I8" s="74">
         <v>0.33</v>
       </c>
-      <c r="J8" s="45">
+      <c r="J8" s="75">
         <v>0.33</v>
       </c>
-      <c r="K8" s="50">
+      <c r="K8" s="76">
         <v>0</v>
       </c>
       <c r="L8" s="4"/>
@@ -1724,35 +1731,35 @@
       <c r="N8" s="4"/>
     </row>
     <row r="9" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="85"/>
+      <c r="A9" s="72"/>
       <c r="B9" s="35" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="26">
         <v>12.273168915897436</v>
       </c>
-      <c r="D9" s="59">
+      <c r="D9" s="46">
         <v>3.5035776248709567</v>
       </c>
-      <c r="E9" s="60">
+      <c r="E9" s="47">
         <v>1.3851353400652622</v>
       </c>
-      <c r="F9" s="61">
-        <v>0</v>
-      </c>
-      <c r="G9" s="60">
+      <c r="F9" s="48">
+        <v>0</v>
+      </c>
+      <c r="G9" s="47">
         <v>0.24443564824681097</v>
       </c>
       <c r="H9" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="I9" s="46">
+      <c r="I9" s="77">
         <v>0.44</v>
       </c>
-      <c r="J9" s="47">
+      <c r="J9" s="78">
         <v>0.44</v>
       </c>
-      <c r="K9" s="48">
+      <c r="K9" s="79">
         <v>0.11</v>
       </c>
       <c r="L9" s="4"/>
@@ -1760,35 +1767,35 @@
       <c r="N9" s="4"/>
     </row>
     <row r="10" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="85"/>
+      <c r="A10" s="72"/>
       <c r="B10" s="35" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="26">
         <v>7.1819852465641034</v>
       </c>
-      <c r="D10" s="59">
-        <v>0</v>
-      </c>
-      <c r="E10" s="60">
+      <c r="D10" s="46">
+        <v>0</v>
+      </c>
+      <c r="E10" s="47">
         <v>0.4177118021002918</v>
       </c>
-      <c r="F10" s="61">
-        <v>0</v>
-      </c>
-      <c r="G10" s="60">
+      <c r="F10" s="48">
+        <v>0</v>
+      </c>
+      <c r="G10" s="47">
         <v>0</v>
       </c>
       <c r="H10" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="I10" s="46">
+      <c r="I10" s="77">
         <v>0.56999999999999995</v>
       </c>
-      <c r="J10" s="47">
+      <c r="J10" s="78">
         <v>0.71</v>
       </c>
-      <c r="K10" s="48">
+      <c r="K10" s="79">
         <v>0</v>
       </c>
       <c r="L10" s="4"/>
@@ -1796,35 +1803,35 @@
       <c r="N10" s="4"/>
     </row>
     <row r="11" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="86"/>
+      <c r="A11" s="73"/>
       <c r="B11" s="36" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="27">
         <v>0.57107699999999995</v>
       </c>
-      <c r="D11" s="55">
-        <v>0</v>
-      </c>
-      <c r="E11" s="62">
-        <v>0</v>
-      </c>
-      <c r="F11" s="63">
-        <v>0</v>
-      </c>
-      <c r="G11" s="62">
+      <c r="D11" s="42">
+        <v>0</v>
+      </c>
+      <c r="E11" s="49">
+        <v>0</v>
+      </c>
+      <c r="F11" s="50">
+        <v>0</v>
+      </c>
+      <c r="G11" s="49">
         <v>0</v>
       </c>
       <c r="H11" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="I11" s="42">
-        <v>0</v>
-      </c>
-      <c r="J11" s="43">
-        <v>0</v>
-      </c>
-      <c r="K11" s="49">
+      <c r="I11" s="80">
+        <v>0</v>
+      </c>
+      <c r="J11" s="81">
+        <v>0</v>
+      </c>
+      <c r="K11" s="82">
         <v>0</v>
       </c>
       <c r="L11" s="4"/>
@@ -1832,7 +1839,7 @@
       <c r="N11" s="4"/>
     </row>
     <row r="12" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="82" t="s">
+      <c r="A12" s="69" t="s">
         <v>25</v>
       </c>
       <c r="B12" s="34" t="s">
@@ -1841,28 +1848,28 @@
       <c r="C12" s="28">
         <v>1.3649733500000001</v>
       </c>
-      <c r="D12" s="64">
+      <c r="D12" s="51">
         <v>5.128305252260053</v>
       </c>
-      <c r="E12" s="65">
-        <v>0</v>
-      </c>
-      <c r="F12" s="66">
-        <v>0</v>
-      </c>
-      <c r="G12" s="65">
+      <c r="E12" s="52">
+        <v>0</v>
+      </c>
+      <c r="F12" s="53">
+        <v>0</v>
+      </c>
+      <c r="G12" s="52">
         <v>0</v>
       </c>
       <c r="H12" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="I12" s="51">
-        <v>0</v>
-      </c>
-      <c r="J12" s="52">
-        <v>0</v>
-      </c>
-      <c r="K12" s="53">
+      <c r="I12" s="83">
+        <v>0</v>
+      </c>
+      <c r="J12" s="84">
+        <v>0</v>
+      </c>
+      <c r="K12" s="85">
         <v>0</v>
       </c>
       <c r="L12" s="4"/>
@@ -1870,35 +1877,35 @@
       <c r="N12" s="4"/>
     </row>
     <row r="13" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="82"/>
+      <c r="A13" s="69"/>
       <c r="B13" s="35" t="s">
         <v>19</v>
       </c>
       <c r="C13" s="26">
         <v>7.5363555180000006</v>
       </c>
-      <c r="D13" s="59">
-        <v>0</v>
-      </c>
-      <c r="E13" s="60">
-        <v>0</v>
-      </c>
-      <c r="F13" s="61">
-        <v>0</v>
-      </c>
-      <c r="G13" s="60">
+      <c r="D13" s="46">
+        <v>0</v>
+      </c>
+      <c r="E13" s="47">
+        <v>0</v>
+      </c>
+      <c r="F13" s="48">
+        <v>0</v>
+      </c>
+      <c r="G13" s="47">
         <v>0.39807039262342825</v>
       </c>
       <c r="H13" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="I13" s="46">
-        <v>0</v>
-      </c>
-      <c r="J13" s="47">
-        <v>0</v>
-      </c>
-      <c r="K13" s="48">
+      <c r="I13" s="77">
+        <v>0</v>
+      </c>
+      <c r="J13" s="78">
+        <v>0</v>
+      </c>
+      <c r="K13" s="79">
         <v>0</v>
       </c>
       <c r="L13" s="4"/>
@@ -1906,35 +1913,35 @@
       <c r="N13" s="4"/>
     </row>
     <row r="14" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="82"/>
+      <c r="A14" s="69"/>
       <c r="B14" s="35" t="s">
         <v>20</v>
       </c>
       <c r="C14" s="26">
         <v>2.1255060000000001</v>
       </c>
-      <c r="D14" s="59">
+      <c r="D14" s="46">
         <v>2.8228572396408196</v>
       </c>
-      <c r="E14" s="60">
+      <c r="E14" s="47">
         <v>1.4114286198204098</v>
       </c>
-      <c r="F14" s="61">
-        <v>0</v>
-      </c>
-      <c r="G14" s="60">
+      <c r="F14" s="48">
+        <v>0</v>
+      </c>
+      <c r="G14" s="47">
         <v>1.4114286198204098</v>
       </c>
       <c r="H14" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="I14" s="46">
-        <v>0</v>
-      </c>
-      <c r="J14" s="47">
-        <v>0</v>
-      </c>
-      <c r="K14" s="48">
+      <c r="I14" s="77">
+        <v>0</v>
+      </c>
+      <c r="J14" s="78">
+        <v>0</v>
+      </c>
+      <c r="K14" s="79">
         <v>0</v>
       </c>
       <c r="L14" s="4"/>
@@ -1942,35 +1949,35 @@
       <c r="N14" s="4"/>
     </row>
     <row r="15" spans="1:15" s="5" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="82"/>
+      <c r="A15" s="69"/>
       <c r="B15" s="35" t="s">
         <v>21</v>
       </c>
       <c r="C15" s="26">
         <v>1.4569589599999999</v>
       </c>
-      <c r="D15" s="59">
+      <c r="D15" s="46">
         <v>4.8045279188921013</v>
       </c>
-      <c r="E15" s="60">
-        <v>0</v>
-      </c>
-      <c r="F15" s="61">
-        <v>0</v>
-      </c>
-      <c r="G15" s="60">
+      <c r="E15" s="47">
+        <v>0</v>
+      </c>
+      <c r="F15" s="48">
+        <v>0</v>
+      </c>
+      <c r="G15" s="47">
         <v>0</v>
       </c>
       <c r="H15" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="I15" s="46">
-        <v>0</v>
-      </c>
-      <c r="J15" s="47">
-        <v>0</v>
-      </c>
-      <c r="K15" s="48">
+      <c r="I15" s="77">
+        <v>0</v>
+      </c>
+      <c r="J15" s="78">
+        <v>0</v>
+      </c>
+      <c r="K15" s="79">
         <v>0</v>
       </c>
       <c r="L15" s="4"/>
@@ -1979,36 +1986,36 @@
       <c r="O15" s="19"/>
     </row>
     <row r="16" spans="1:15" s="5" customFormat="1" ht="15.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="83"/>
+      <c r="A16" s="70"/>
       <c r="B16" s="38" t="s">
         <v>22</v>
       </c>
       <c r="C16" s="27">
         <v>5.7995670199999996</v>
       </c>
-      <c r="D16" s="55">
-        <v>0</v>
-      </c>
-      <c r="E16" s="62">
-        <v>0</v>
-      </c>
-      <c r="F16" s="63">
+      <c r="D16" s="42">
+        <v>0</v>
+      </c>
+      <c r="E16" s="49">
+        <v>0</v>
+      </c>
+      <c r="F16" s="50">
         <f>[1]Sheet1!$AT$18</f>
         <v>0.17242666505128171</v>
       </c>
-      <c r="G16" s="62">
+      <c r="G16" s="49">
         <v>0</v>
       </c>
       <c r="H16" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="I16" s="42">
+      <c r="I16" s="80">
         <v>1</v>
       </c>
-      <c r="J16" s="43">
-        <v>0</v>
-      </c>
-      <c r="K16" s="49">
+      <c r="J16" s="81">
+        <v>0</v>
+      </c>
+      <c r="K16" s="82">
         <v>0</v>
       </c>
       <c r="L16" s="4"/>
@@ -2016,35 +2023,35 @@
       <c r="N16" s="4"/>
     </row>
     <row r="17" spans="1:28" s="8" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="78"/>
+      <c r="A17" s="65"/>
       <c r="B17" s="17" t="s">
         <v>30</v>
       </c>
       <c r="C17" s="18">
         <v>86.97332109200002</v>
       </c>
-      <c r="D17" s="54">
+      <c r="D17" s="41">
         <v>0.3449333614415635</v>
       </c>
-      <c r="E17" s="54">
+      <c r="E17" s="41">
         <v>0.3449333614415635</v>
       </c>
-      <c r="F17" s="54">
+      <c r="F17" s="41">
         <v>0.3449333614415635</v>
       </c>
-      <c r="G17" s="54">
+      <c r="G17" s="41">
         <v>0.3449333614415635</v>
       </c>
       <c r="H17" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="I17" s="41">
+      <c r="I17" s="86">
         <v>0.25</v>
       </c>
-      <c r="J17" s="41">
+      <c r="J17" s="86">
         <v>0.25</v>
       </c>
-      <c r="K17" s="41">
+      <c r="K17" s="86">
         <v>0.25</v>
       </c>
       <c r="L17" s="7"/>
@@ -2066,7 +2073,7 @@
       <c r="AB17" s="7"/>
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A18" s="79"/>
+      <c r="A18" s="66"/>
     </row>
     <row r="19" spans="1:28" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="10"/>
